--- a/Data/Hires/Workday_NewHire_Slovakia_Regression_PK17.xlsx
+++ b/Data/Hires/Workday_NewHire_Slovakia_Regression_PK17.xlsx
@@ -1,20 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{00EF08DC-052D-41D9-B941-7746A949D8E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="380" windowWidth="14400" windowHeight="7360"/>
+    <workbookView xWindow="1900" yWindow="1900" windowWidth="14400" windowHeight="7360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Sheet2" state="visible" r:id="rId4"/>
+    <sheet name="Sheet2" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="133">
   <si>
     <t>TestCaseIDs</t>
   </si>
@@ -235,12 +250,6 @@
     <t>Test1</t>
   </si>
   <si>
-    <t>10698890</t>
-  </si>
-  <si>
-    <t>Passed</t>
-  </si>
-  <si>
     <t>870 Recruitment (Wazup Zudimi (9581610))</t>
   </si>
   <si>
@@ -319,7 +328,7 @@
     <t>SK Monthly</t>
   </si>
   <si>
-    <t xml:space="preserve">Meal Voucher Card </t>
+    <t>Meal Voucher Card </t>
   </si>
   <si>
     <t>Všeobecná zdrav. Poisť.</t>
@@ -381,9 +390,6 @@
   </si>
   <si>
     <t>Test2</t>
-  </si>
-  <si>
-    <t>10698891</t>
   </si>
   <si>
     <t>870 Store Management (Wazup Zudimi (9581610))</t>
@@ -428,43 +434,43 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <color rgb="FFFF0000"/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <family val="2"/>
-      <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <color theme="1"/>
-      <family val="2"/>
-      <sz val="14"/>
-      <name val="Arial"/>
     </font>
     <font>
       <u/>
+      <sz val="11"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="5">
@@ -476,7 +482,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.5999938962981048"/>
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -487,7 +493,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.7999816888943144"/>
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -507,17 +513,27 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -527,15 +543,25 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin"/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -546,7 +572,9 @@
         <color indexed="64"/>
       </right>
       <top/>
-      <bottom style="thin"/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -556,31 +584,49 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin"/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
       <top/>
-      <bottom style="thin"/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -975,9 +1021,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:CH3"/>
-  <sheetFormatPr defaultRowHeight="15.65" outlineLevelRow="1" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="15.65" customHeight="1" outlineLevelRow="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="10.81640625" style="1" customWidth="1"/>
     <col min="3" max="3" width="9.36328125" style="1" customWidth="1"/>
@@ -1067,7 +1113,7 @@
     <col min="87" max="87" width="8.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.5" customHeight="1" spans="1:86" s="3" customFormat="1" x14ac:dyDescent="0.25" outlineLevel="1" collapsed="1">
+    <row r="1" spans="1:86" s="3" customFormat="1" ht="14.5" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1305,45 +1351,40 @@
       <c r="CG1" s="11"/>
       <c r="CH1" s="12"/>
     </row>
-    <row r="2" ht="15.65" customHeight="1" spans="1:86" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:86" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="13"/>
+      <c r="D2" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="E2" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="D2" s="14" t="s">
+      <c r="F2" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="E2" s="15" t="s">
+      <c r="G2" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="F2" s="16" t="s">
+      <c r="H2" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="G2" s="17" t="s">
+      <c r="I2" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="H2" s="15" t="s">
+      <c r="J2" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="I2" s="18" t="s">
+      <c r="K2" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="J2" s="18" t="s">
+      <c r="L2" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="M2" s="18" t="s">
         <v>81</v>
-      </c>
-      <c r="K2" s="19" t="s">
-        <v>82</v>
-      </c>
-      <c r="L2" s="15" t="s">
-        <v>76</v>
-      </c>
-      <c r="M2" s="18" t="s">
-        <v>83</v>
       </c>
       <c r="N2" s="18">
         <v>1</v>
@@ -1355,188 +1396,188 @@
         <v>90851</v>
       </c>
       <c r="Q2" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="R2" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="S2" s="18" t="s">
+        <v>79</v>
+      </c>
+      <c r="T2" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="U2" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="R2" s="18" t="s">
-        <v>76</v>
-      </c>
-      <c r="S2" s="18" t="s">
-        <v>81</v>
-      </c>
-      <c r="T2" s="19" t="s">
+      <c r="V2" s="18" t="s">
+        <v>79</v>
+      </c>
+      <c r="W2" s="21">
+        <f t="shared" ref="W2:W3" ca="1" si="0">TODAY()-31</f>
+        <v>45761</v>
+      </c>
+      <c r="X2" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="U2" s="20" t="s">
+      <c r="Y2" s="22" t="s">
         <v>86</v>
       </c>
-      <c r="V2" s="18" t="s">
-        <v>81</v>
-      </c>
-      <c r="W2" s="21">
-        <f t="shared" ref="W2:W3" si="0">TODAY()-31</f>
-        <v>45751</v>
-      </c>
-      <c r="X2" s="18" t="s">
+      <c r="Z2" s="23" t="s">
         <v>87</v>
       </c>
-      <c r="Y2" s="22" t="s">
+      <c r="AA2" s="24" t="s">
         <v>88</v>
       </c>
-      <c r="Z2" s="23" t="s">
+      <c r="AB2" s="19" t="s">
         <v>89</v>
-      </c>
-      <c r="AA2" s="24" t="s">
-        <v>90</v>
-      </c>
-      <c r="AB2" s="19" t="s">
-        <v>91</v>
       </c>
       <c r="AC2" s="15">
         <v>870</v>
       </c>
       <c r="AD2" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE2" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="AF2" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="AG2" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="AE2" s="15" t="s">
+      <c r="AH2" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="AF2" s="23" t="s">
-        <v>82</v>
-      </c>
-      <c r="AG2" s="15" t="s">
+      <c r="AI2" s="21">
+        <f ca="1">TODAY()+365</f>
+        <v>46157</v>
+      </c>
+      <c r="AJ2" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="AH2" s="15" t="s">
+      <c r="AK2" s="25" t="s">
         <v>95</v>
       </c>
-      <c r="AI2" s="21">
-        <f>TODAY()+365</f>
-        <v>46147</v>
-      </c>
-      <c r="AJ2" s="18" t="s">
+      <c r="AL2" s="25" t="s">
         <v>96</v>
       </c>
-      <c r="AK2" s="25" t="s">
+      <c r="AM2" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="AL2" s="25" t="s">
+      <c r="AN2" s="18" t="s">
         <v>98</v>
       </c>
-      <c r="AM2" s="18" t="s">
+      <c r="AO2" s="24" t="s">
         <v>99</v>
       </c>
-      <c r="AN2" s="18" t="s">
+      <c r="AP2" s="26" t="s">
         <v>100</v>
       </c>
-      <c r="AO2" s="24" t="s">
+      <c r="AQ2" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="AR2" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="AS2" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="AT2" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="AU2" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="AV2" s="26" t="s">
         <v>101</v>
       </c>
-      <c r="AP2" s="26" t="s">
+      <c r="AW2" s="26" t="s">
         <v>102</v>
-      </c>
-      <c r="AQ2" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="AR2" s="19" t="s">
-        <v>82</v>
-      </c>
-      <c r="AS2" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="AT2" s="19" t="s">
-        <v>82</v>
-      </c>
-      <c r="AU2" s="19" t="s">
-        <v>82</v>
-      </c>
-      <c r="AV2" s="26" t="s">
-        <v>103</v>
-      </c>
-      <c r="AW2" s="26" t="s">
-        <v>104</v>
       </c>
       <c r="AX2" s="27">
         <v>1234567891</v>
       </c>
       <c r="AY2" s="15" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="AZ2" s="21" t="s">
+        <v>103</v>
+      </c>
+      <c r="BA2" s="19">
+        <f t="shared" ref="BA2:BA3" ca="1" si="1">TODAY()+90</f>
+        <v>45882</v>
+      </c>
+      <c r="BB2" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="BC2" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="BA2" s="19">
-        <f t="shared" ref="BA2:BA3" si="1">TODAY()+90</f>
-        <v>45872</v>
-      </c>
-      <c r="BB2" s="15" t="s">
+      <c r="BD2" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="BC2" s="18" t="s">
+      <c r="BE2" s="18" t="s">
         <v>107</v>
       </c>
-      <c r="BD2" s="15" t="s">
+      <c r="BF2" s="19">
+        <f t="shared" ref="BF2:BF3" ca="1" si="2">W2</f>
+        <v>45761</v>
+      </c>
+      <c r="BG2" s="19">
+        <f t="shared" ref="BG2:BG3" ca="1" si="3">W2</f>
+        <v>45761</v>
+      </c>
+      <c r="BH2" s="21">
+        <f t="shared" ref="BH2:BH3" ca="1" si="4">AI2</f>
+        <v>46157</v>
+      </c>
+      <c r="BI2" s="28" t="s">
+        <v>74</v>
+      </c>
+      <c r="BJ2" s="29" t="s">
         <v>108</v>
       </c>
-      <c r="BE2" s="18" t="s">
+      <c r="BK2" s="30">
+        <f t="array" aca="1" ref="BK2:BK3" ca="1">_xlfn.RANDARRAY(2,1,123456789,999999999,TRUE)</f>
+        <v>497291593</v>
+      </c>
+      <c r="BL2" s="31" t="s">
         <v>109</v>
       </c>
-      <c r="BF2" s="19">
-        <f t="shared" ref="BF2:BF3" si="2">W2</f>
-        <v>45751</v>
-      </c>
-      <c r="BG2" s="19">
-        <f t="shared" ref="BG2:BG3" si="3">W2</f>
-        <v>45751</v>
-      </c>
-      <c r="BH2" s="21">
-        <f t="shared" ref="BH2:BH3" si="4">AI2</f>
-        <v>46147</v>
-      </c>
-      <c r="BI2" s="28" t="s">
-        <v>76</v>
-      </c>
-      <c r="BJ2" s="29" t="s">
+      <c r="BM2" s="19" t="s">
         <v>110</v>
       </c>
-      <c r="BK2" s="30">
-        <f t="array" ref="BK2:BK3">_xlfn.RANDARRAY(2,1,123456789,999999999,TRUE)</f>
-        <v>202925705</v>
-      </c>
-      <c r="BL2" s="31" t="s">
+      <c r="BN2" s="28" t="s">
         <v>111</v>
       </c>
-      <c r="BM2" s="19" t="s">
+      <c r="BO2" s="28" t="s">
         <v>112</v>
       </c>
-      <c r="BN2" s="28" t="s">
+      <c r="BP2" s="32" t="s">
+        <v>80</v>
+      </c>
+      <c r="BQ2" s="28" t="s">
         <v>113</v>
       </c>
-      <c r="BO2" s="28" t="s">
+      <c r="BR2" s="28" t="s">
+        <v>74</v>
+      </c>
+      <c r="BS2" s="15" t="s">
         <v>114</v>
       </c>
-      <c r="BP2" s="32" t="s">
-        <v>82</v>
-      </c>
-      <c r="BQ2" s="28" t="s">
+      <c r="BT2" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="BR2" s="28" t="s">
-        <v>76</v>
-      </c>
-      <c r="BS2" s="15" t="s">
+      <c r="BU2" s="28" t="s">
         <v>116</v>
       </c>
-      <c r="BT2" s="15" t="s">
+      <c r="BV2" s="28" t="s">
         <v>117</v>
       </c>
-      <c r="BU2" s="28" t="s">
+      <c r="BW2" s="28" t="s">
         <v>118</v>
-      </c>
-      <c r="BV2" s="28" t="s">
-        <v>119</v>
-      </c>
-      <c r="BW2" s="28" t="s">
-        <v>120</v>
       </c>
       <c r="BX2" s="33"/>
       <c r="BY2" s="33"/>
@@ -1550,45 +1591,41 @@
       <c r="CG2" s="33"/>
       <c r="CH2" s="33"/>
     </row>
-    <row r="3" ht="15.65" customHeight="1" spans="1:86" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:86" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B3" s="35"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="F3" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="B3" s="35" t="s">
+      <c r="G3" s="17" t="s">
         <v>122</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="H3" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="I3" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="J3" s="18" t="s">
+        <v>79</v>
+      </c>
+      <c r="K3" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="L3" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="D3" s="14" t="s">
-        <v>123</v>
-      </c>
-      <c r="E3" s="15" t="s">
-        <v>76</v>
-      </c>
-      <c r="F3" s="16" t="s">
-        <v>124</v>
-      </c>
-      <c r="G3" s="17" t="s">
-        <v>125</v>
-      </c>
-      <c r="H3" s="15" t="s">
-        <v>79</v>
-      </c>
-      <c r="I3" s="18" t="s">
-        <v>80</v>
-      </c>
-      <c r="J3" s="18" t="s">
+      <c r="M3" s="18" t="s">
         <v>81</v>
-      </c>
-      <c r="K3" s="19" t="s">
-        <v>82</v>
-      </c>
-      <c r="L3" s="15" t="s">
-        <v>76</v>
-      </c>
-      <c r="M3" s="18" t="s">
-        <v>83</v>
       </c>
       <c r="N3" s="18">
         <v>1</v>
@@ -1600,47 +1637,47 @@
         <v>90851</v>
       </c>
       <c r="Q3" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="R3" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="S3" s="18" t="s">
+        <v>79</v>
+      </c>
+      <c r="T3" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="U3" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="R3" s="18" t="s">
-        <v>76</v>
-      </c>
-      <c r="S3" s="18" t="s">
-        <v>81</v>
-      </c>
-      <c r="T3" s="19" t="s">
+      <c r="V3" s="18" t="s">
+        <v>79</v>
+      </c>
+      <c r="W3" s="21">
+        <f t="shared" ca="1" si="0"/>
+        <v>45761</v>
+      </c>
+      <c r="X3" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="U3" s="20" t="s">
-        <v>86</v>
-      </c>
-      <c r="V3" s="18" t="s">
-        <v>81</v>
-      </c>
-      <c r="W3" s="21">
-        <f t="shared" si="0"/>
-        <v>45751</v>
-      </c>
-      <c r="X3" s="18" t="s">
-        <v>87</v>
-      </c>
       <c r="Y3" s="22" t="s">
+        <v>123</v>
+      </c>
+      <c r="Z3" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="AA3" s="24" t="s">
+        <v>125</v>
+      </c>
+      <c r="AB3" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="AC3" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="Z3" s="15" t="s">
-        <v>127</v>
-      </c>
-      <c r="AA3" s="24" t="s">
-        <v>128</v>
-      </c>
-      <c r="AB3" s="19" t="s">
-        <v>91</v>
-      </c>
-      <c r="AC3" s="15" t="s">
-        <v>129</v>
-      </c>
       <c r="AD3" s="15" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="AE3" s="15">
         <v>40</v>
@@ -1649,137 +1686,138 @@
         <v>40</v>
       </c>
       <c r="AG3" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="AH3" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="AI3" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="AJ3" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="AH3" s="15" t="s">
-        <v>95</v>
-      </c>
-      <c r="AI3" s="21" t="s">
-        <v>82</v>
-      </c>
-      <c r="AJ3" s="18" t="s">
-        <v>96</v>
-      </c>
       <c r="AK3" s="25" t="s">
+        <v>127</v>
+      </c>
+      <c r="AL3" s="25" t="s">
+        <v>128</v>
+      </c>
+      <c r="AM3" s="18" t="s">
+        <v>97</v>
+      </c>
+      <c r="AN3" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="AO3" s="24" t="s">
+        <v>129</v>
+      </c>
+      <c r="AP3" s="26" t="s">
         <v>130</v>
       </c>
-      <c r="AL3" s="25" t="s">
+      <c r="AQ3" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="AR3" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="AS3" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="AT3" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="AU3" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="AV3" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="AW3" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="AX3" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="AY3" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="AZ3" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="BA3" s="19">
+        <f t="shared" ca="1" si="1"/>
+        <v>45882</v>
+      </c>
+      <c r="BB3" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="BC3" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="BD3" s="15" t="s">
         <v>131</v>
       </c>
-      <c r="AM3" s="18" t="s">
-        <v>99</v>
-      </c>
-      <c r="AN3" s="18" t="s">
-        <v>100</v>
-      </c>
-      <c r="AO3" s="24" t="s">
+      <c r="BE3" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="BF3" s="19">
+        <f t="shared" ca="1" si="2"/>
+        <v>45761</v>
+      </c>
+      <c r="BG3" s="19">
+        <f t="shared" ca="1" si="3"/>
+        <v>45761</v>
+      </c>
+      <c r="BH3" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v>N/A</v>
+      </c>
+      <c r="BI3" s="28" t="s">
+        <v>74</v>
+      </c>
+      <c r="BJ3" s="29" t="s">
+        <v>108</v>
+      </c>
+      <c r="BK3" s="30">
+        <f ca="1"/>
+        <v>392642536</v>
+      </c>
+      <c r="BL3" s="31" t="s">
         <v>132</v>
       </c>
-      <c r="AP3" s="26" t="s">
-        <v>133</v>
-      </c>
-      <c r="AQ3" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="AR3" s="19" t="s">
-        <v>82</v>
-      </c>
-      <c r="AS3" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="AT3" s="19" t="s">
-        <v>82</v>
-      </c>
-      <c r="AU3" s="19" t="s">
-        <v>82</v>
-      </c>
-      <c r="AV3" s="26" t="s">
-        <v>82</v>
-      </c>
-      <c r="AW3" s="26" t="s">
-        <v>82</v>
-      </c>
-      <c r="AX3" s="26" t="s">
-        <v>82</v>
-      </c>
-      <c r="AY3" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="AZ3" s="21" t="s">
-        <v>82</v>
-      </c>
-      <c r="BA3" s="19">
-        <f t="shared" si="1"/>
-        <v>45872</v>
-      </c>
-      <c r="BB3" s="15" t="s">
-        <v>106</v>
-      </c>
-      <c r="BC3" s="18" t="s">
-        <v>107</v>
-      </c>
-      <c r="BD3" s="15" t="s">
-        <v>134</v>
-      </c>
-      <c r="BE3" s="18" t="s">
-        <v>109</v>
-      </c>
-      <c r="BF3" s="19">
-        <f t="shared" si="2"/>
-        <v>45751</v>
-      </c>
-      <c r="BG3" s="19">
-        <f t="shared" si="3"/>
-        <v>45751</v>
-      </c>
-      <c r="BH3" s="21">
-        <f t="shared" si="4"/>
-        <v>NaN</v>
-      </c>
-      <c r="BI3" s="28" t="s">
-        <v>76</v>
-      </c>
-      <c r="BJ3" s="29" t="s">
+      <c r="BM3" s="19" t="s">
         <v>110</v>
       </c>
-      <c r="BK3" s="30">
-        <v>811320403</v>
-      </c>
-      <c r="BL3" s="31" t="s">
-        <v>135</v>
-      </c>
-      <c r="BM3" s="19" t="s">
+      <c r="BN3" s="28" t="s">
+        <v>111</v>
+      </c>
+      <c r="BO3" s="28" t="s">
         <v>112</v>
       </c>
-      <c r="BN3" s="28" t="s">
+      <c r="BP3" s="32" t="s">
+        <v>80</v>
+      </c>
+      <c r="BQ3" s="28" t="s">
         <v>113</v>
       </c>
-      <c r="BO3" s="28" t="s">
+      <c r="BR3" s="28" t="s">
+        <v>74</v>
+      </c>
+      <c r="BS3" s="15" t="s">
         <v>114</v>
       </c>
-      <c r="BP3" s="32" t="s">
-        <v>82</v>
-      </c>
-      <c r="BQ3" s="28" t="s">
+      <c r="BT3" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="BR3" s="28" t="s">
-        <v>76</v>
-      </c>
-      <c r="BS3" s="15" t="s">
+      <c r="BU3" s="28" t="s">
         <v>116</v>
       </c>
-      <c r="BT3" s="15" t="s">
+      <c r="BV3" s="28" t="s">
         <v>117</v>
       </c>
-      <c r="BU3" s="28" t="s">
+      <c r="BW3" s="28" t="s">
         <v>118</v>
-      </c>
-      <c r="BV3" s="28" t="s">
-        <v>119</v>
-      </c>
-      <c r="BW3" s="28" t="s">
-        <v>120</v>
       </c>
       <c r="BX3" s="33"/>
       <c r="BY3" s="33"/>
@@ -1794,35 +1832,17 @@
       <c r="CH3" s="33"/>
     </row>
   </sheetData>
-  <dataValidations count="7">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BE2:BE3">
-      <formula1>INDIRECT($H2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BU2:BU3">
-      <formula1>INDIRECT($H2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CB2:CB3">
-      <formula1>INDIRECT($H2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J3">
-      <formula1>INDIRECT($H2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S3">
-      <formula1>INDIRECT($H2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V2:V3">
-      <formula1>INDIRECT($H2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X2:X3">
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BE2:BE3 X2:X3 V2:V3 S2:S3 J2:J3 CB2:CB3 BU2:BU3" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>INDIRECT($H2)</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="U2" r:id="rId1"/>
-    <hyperlink ref="U3" r:id="rId2"/>
+    <hyperlink ref="U2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="U3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
   <headerFooter>
     <oddFooter>&amp;L_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 EXPLEO Internal</oddFooter>
   </headerFooter>

--- a/Data/Hires/Workday_NewHire_Slovakia_Regression_PK17.xlsx
+++ b/Data/Hires/Workday_NewHire_Slovakia_Regression_PK17.xlsx
@@ -1,35 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{00EF08DC-052D-41D9-B941-7746A949D8E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="1900" yWindow="1900" windowWidth="14400" windowHeight="7360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1900" yWindow="1900" windowWidth="14400" windowHeight="7360"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet2" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Sheet2" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="136">
   <si>
     <t>TestCaseIDs</t>
   </si>
@@ -250,16 +235,22 @@
     <t>Test1</t>
   </si>
   <si>
+    <t>10699090</t>
+  </si>
+  <si>
+    <t>Passed</t>
+  </si>
+  <si>
     <t>870 Recruitment (Wazup Zudimi (9581610))</t>
   </si>
   <si>
     <t>Slovakia</t>
   </si>
   <si>
-    <t>Rosemarie</t>
-  </si>
-  <si>
-    <t>Collins</t>
+    <t>Einar</t>
+  </si>
+  <si>
+    <t>Metz</t>
   </si>
   <si>
     <t>041/562 66 84</t>
@@ -328,7 +319,7 @@
     <t>SK Monthly</t>
   </si>
   <si>
-    <t>Meal Voucher Card </t>
+    <t xml:space="preserve">Meal Voucher Card </t>
   </si>
   <si>
     <t>Všeobecná zdrav. Poisť.</t>
@@ -392,16 +383,19 @@
     <t>Test2</t>
   </si>
   <si>
+    <t>10699091</t>
+  </si>
+  <si>
     <t>870 Store Management (Wazup Zudimi (9581610))</t>
   </si>
   <si>
-    <t>Kade</t>
-  </si>
-  <si>
-    <t>Lebsack</t>
-  </si>
-  <si>
-    <t>Auto 86412752</t>
+    <t>Werner</t>
+  </si>
+  <si>
+    <t>Welch</t>
+  </si>
+  <si>
+    <t>Auto 90126088</t>
   </si>
   <si>
     <t>Permanent</t>
@@ -434,43 +428,43 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
+      <family val="2"/>
+      <scheme val="minor"/>
       <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
+      <color theme="1"/>
+      <family val="2"/>
       <sz val="14"/>
-      <color theme="1"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <u/>
+      <family val="2"/>
+      <scheme val="minor"/>
       <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
@@ -482,7 +476,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
+        <fgColor theme="5" tint="0.5999938962981048"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -493,7 +487,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
+        <fgColor theme="5" tint="0.7999816888943144"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -513,27 +507,17 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
@@ -543,25 +527,15 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
+      <top style="thin"/>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
@@ -572,9 +546,7 @@
         <color indexed="64"/>
       </right>
       <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
@@ -584,49 +556,31 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
+      <top style="thin"/>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
+      <left style="thin"/>
+      <right style="thin"/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
+      <left style="thin"/>
+      <right style="thin"/>
       <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
@@ -1021,9 +975,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:CH3"/>
-  <sheetFormatPr defaultRowHeight="15.65" customHeight="1" outlineLevelRow="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15.65" outlineLevelRow="1" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="10.81640625" style="1" customWidth="1"/>
     <col min="3" max="3" width="9.36328125" style="1" customWidth="1"/>
@@ -1113,7 +1067,7 @@
     <col min="87" max="87" width="8.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:86" s="3" customFormat="1" ht="14.5" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="14.5" customHeight="1" spans="1:86" s="3" customFormat="1" x14ac:dyDescent="0.25" outlineLevel="1" collapsed="1">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1351,40 +1305,45 @@
       <c r="CG1" s="11"/>
       <c r="CH1" s="12"/>
     </row>
-    <row r="2" spans="1:86" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" ht="15.65" customHeight="1" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="C2" s="13"/>
+      <c r="B2" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>74</v>
+      </c>
       <c r="D2" s="14" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F2" s="16" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G2" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="H2" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="I2" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="J2" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="K2" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="L2" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="H2" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="I2" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="J2" s="18" t="s">
-        <v>79</v>
-      </c>
-      <c r="K2" s="19" t="s">
-        <v>80</v>
-      </c>
-      <c r="L2" s="15" t="s">
-        <v>74</v>
-      </c>
       <c r="M2" s="18" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="N2" s="18">
         <v>1</v>
@@ -1396,188 +1355,188 @@
         <v>90851</v>
       </c>
       <c r="Q2" s="18" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="R2" s="18" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="S2" s="18" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="T2" s="19" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="U2" s="20" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="V2" s="18" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="W2" s="21">
-        <f t="shared" ref="W2:W3" ca="1" si="0">TODAY()-31</f>
+        <f t="shared" ref="W2:W3" si="0">TODAY()-31</f>
         <v>45761</v>
       </c>
       <c r="X2" s="18" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="Y2" s="22" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="Z2" s="23" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AA2" s="24" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AB2" s="19" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AC2" s="15">
         <v>870</v>
       </c>
       <c r="AD2" s="15" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AE2" s="15" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AF2" s="23" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AG2" s="15" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AH2" s="15" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AI2" s="21">
-        <f ca="1">TODAY()+365</f>
+        <f>TODAY()+365</f>
         <v>46157</v>
       </c>
       <c r="AJ2" s="18" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AK2" s="25" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="AL2" s="25" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AM2" s="18" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AN2" s="18" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AO2" s="24" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="AP2" s="26" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AQ2" s="15" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="AR2" s="19" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AS2" s="15" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="AT2" s="19" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AU2" s="19" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AV2" s="26" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AW2" s="26" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AX2" s="27">
         <v>1234567891</v>
       </c>
       <c r="AY2" s="15" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="AZ2" s="21" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="BA2" s="19">
-        <f t="shared" ref="BA2:BA3" ca="1" si="1">TODAY()+90</f>
+        <f t="shared" ref="BA2:BA3" si="1">TODAY()+90</f>
         <v>45882</v>
       </c>
       <c r="BB2" s="15" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="BC2" s="18" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="BD2" s="15" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="BE2" s="18" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="BF2" s="19">
-        <f t="shared" ref="BF2:BF3" ca="1" si="2">W2</f>
+        <f t="shared" ref="BF2:BF3" si="2">W2</f>
         <v>45761</v>
       </c>
       <c r="BG2" s="19">
-        <f t="shared" ref="BG2:BG3" ca="1" si="3">W2</f>
+        <f t="shared" ref="BG2:BG3" si="3">W2</f>
         <v>45761</v>
       </c>
       <c r="BH2" s="21">
-        <f t="shared" ref="BH2:BH3" ca="1" si="4">AI2</f>
+        <f t="shared" ref="BH2:BH3" si="4">AI2</f>
         <v>46157</v>
       </c>
       <c r="BI2" s="28" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="BJ2" s="29" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="BK2" s="30">
-        <f t="array" aca="1" ref="BK2:BK3" ca="1">_xlfn.RANDARRAY(2,1,123456789,999999999,TRUE)</f>
+        <f t="array" ref="BK2:BK3">_xlfn.RANDARRAY(2,1,123456789,999999999,TRUE)</f>
         <v>497291593</v>
       </c>
       <c r="BL2" s="31" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="BM2" s="19" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="BN2" s="28" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="BO2" s="28" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="BP2" s="32" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="BQ2" s="28" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="BR2" s="28" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="BS2" s="15" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="BT2" s="15" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="BU2" s="28" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="BV2" s="28" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="BW2" s="28" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="BX2" s="33"/>
       <c r="BY2" s="33"/>
@@ -1591,41 +1550,45 @@
       <c r="CG2" s="33"/>
       <c r="CH2" s="33"/>
     </row>
-    <row r="3" spans="1:86" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" ht="15.65" customHeight="1" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="B3" s="35"/>
-      <c r="C3" s="13"/>
+        <v>121</v>
+      </c>
+      <c r="B3" s="35" t="s">
+        <v>122</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>74</v>
+      </c>
       <c r="D3" s="14" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="G3" s="17" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="I3" s="18" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="J3" s="18" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K3" s="19" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="L3" s="15" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M3" s="18" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="N3" s="18">
         <v>1</v>
@@ -1637,47 +1600,47 @@
         <v>90851</v>
       </c>
       <c r="Q3" s="18" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="R3" s="18" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="S3" s="18" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="T3" s="19" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="U3" s="20" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="V3" s="18" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="W3" s="21">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>45761</v>
       </c>
       <c r="X3" s="18" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="Y3" s="22" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="Z3" s="15" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="AA3" s="24" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="AB3" s="19" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AC3" s="15" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="AD3" s="15" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AE3" s="15">
         <v>40</v>
@@ -1686,138 +1649,137 @@
         <v>40</v>
       </c>
       <c r="AG3" s="15" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AH3" s="15" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AI3" s="21" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AJ3" s="18" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AK3" s="25" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="AL3" s="25" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="AM3" s="18" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AN3" s="18" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AO3" s="24" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="AP3" s="26" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="AQ3" s="15" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="AR3" s="19" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AS3" s="15" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="AT3" s="19" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AU3" s="19" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AV3" s="26" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AW3" s="26" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AX3" s="26" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AY3" s="15" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="AZ3" s="21" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="BA3" s="19">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" si="1"/>
         <v>45882</v>
       </c>
       <c r="BB3" s="15" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="BC3" s="18" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="BD3" s="15" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="BE3" s="18" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="BF3" s="19">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" si="2"/>
         <v>45761</v>
       </c>
       <c r="BG3" s="19">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" si="3"/>
         <v>45761</v>
       </c>
-      <c r="BH3" s="21" t="str">
+      <c r="BH3" s="21">
         <f t="shared" si="4"/>
-        <v>N/A</v>
+        <v>NaN</v>
       </c>
       <c r="BI3" s="28" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="BJ3" s="29" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="BK3" s="30">
-        <f ca="1"/>
         <v>392642536</v>
       </c>
       <c r="BL3" s="31" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="BM3" s="19" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="BN3" s="28" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="BO3" s="28" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="BP3" s="32" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="BQ3" s="28" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="BR3" s="28" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="BS3" s="15" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="BT3" s="15" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="BU3" s="28" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="BV3" s="28" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="BW3" s="28" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="BX3" s="33"/>
       <c r="BY3" s="33"/>
@@ -1832,17 +1794,35 @@
       <c r="CH3" s="33"/>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BE2:BE3 X2:X3 V2:V3 S2:S3 J2:J3 CB2:CB3 BU2:BU3" xr:uid="{00000000-0002-0000-0000-000000000000}">
+  <dataValidations count="7">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BE2:BE3">
+      <formula1>INDIRECT($H2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BU2:BU3">
+      <formula1>INDIRECT($H2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CB2:CB3">
+      <formula1>INDIRECT($H2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J3">
+      <formula1>INDIRECT($H2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S3">
+      <formula1>INDIRECT($H2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V2:V3">
+      <formula1>INDIRECT($H2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X2:X3">
       <formula1>INDIRECT($H2)</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="U2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="U3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="U2" r:id="rId1"/>
+    <hyperlink ref="U3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
   <headerFooter>
     <oddFooter>&amp;L_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 EXPLEO Internal</oddFooter>
   </headerFooter>

--- a/Data/Hires/Workday_NewHire_Slovakia_Regression_PK17.xlsx
+++ b/Data/Hires/Workday_NewHire_Slovakia_Regression_PK17.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="380" windowWidth="14400" windowHeight="7360"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420"/>
   </bookViews>
   <sheets>
     <sheet sheetId="1" name="Sheet2" state="visible" r:id="rId4"/>
@@ -235,7 +235,7 @@
     <t>Test1</t>
   </si>
   <si>
-    <t>10698890</t>
+    <t>10699227</t>
   </si>
   <si>
     <t>Passed</t>
@@ -247,10 +247,10 @@
     <t>Slovakia</t>
   </si>
   <si>
-    <t>Rosemarie</t>
-  </si>
-  <si>
-    <t>Collins</t>
+    <t>Tremayne</t>
+  </si>
+  <si>
+    <t>Feest</t>
   </si>
   <si>
     <t>041/562 66 84</t>
@@ -383,19 +383,19 @@
     <t>Test2</t>
   </si>
   <si>
-    <t>10698891</t>
+    <t>10699226</t>
   </si>
   <si>
     <t>870 Store Management (Wazup Zudimi (9581610))</t>
   </si>
   <si>
-    <t>Kade</t>
-  </si>
-  <si>
-    <t>Lebsack</t>
-  </si>
-  <si>
-    <t>Auto 86412752</t>
+    <t>Felicity</t>
+  </si>
+  <si>
+    <t>Beer</t>
+  </si>
+  <si>
+    <t>Auto 53216452</t>
   </si>
   <si>
     <t>Permanent</t>
@@ -979,7 +979,8 @@
   <dimension ref="A1:CH3"/>
   <sheetFormatPr defaultRowHeight="15.65" outlineLevelRow="1" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
   <cols>
-    <col min="1" max="2" width="10.81640625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="10.81640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="58.36328125" style="1" customWidth="1"/>
     <col min="3" max="3" width="9.36328125" style="1" customWidth="1"/>
     <col min="4" max="4" width="21.453125" style="1" customWidth="1"/>
     <col min="5" max="5" width="7.54296875" style="1" customWidth="1"/>
@@ -1039,7 +1040,7 @@
     <col min="59" max="59" width="18.26953125" style="1" customWidth="1"/>
     <col min="60" max="60" width="15.08984375" style="1" customWidth="1"/>
     <col min="61" max="61" width="8.453125" style="1" customWidth="1"/>
-    <col min="62" max="62" width="21.7265625" style="1" customWidth="1"/>
+    <col min="62" max="62" width="50.54296875" style="1" customWidth="1"/>
     <col min="63" max="63" width="26.36328125" style="1" customWidth="1"/>
     <col min="64" max="64" width="7" style="1" customWidth="1"/>
     <col min="65" max="65" width="10.7265625" style="1" customWidth="1"/>
@@ -1374,7 +1375,7 @@
       </c>
       <c r="W2" s="21">
         <f t="shared" ref="W2:W3" si="0">TODAY()-31</f>
-        <v>45751</v>
+        <v>45767</v>
       </c>
       <c r="X2" s="18" t="s">
         <v>87</v>
@@ -1411,7 +1412,7 @@
       </c>
       <c r="AI2" s="21">
         <f>TODAY()+365</f>
-        <v>46147</v>
+        <v>46163</v>
       </c>
       <c r="AJ2" s="18" t="s">
         <v>96</v>
@@ -1466,7 +1467,7 @@
       </c>
       <c r="BA2" s="19">
         <f t="shared" ref="BA2:BA3" si="1">TODAY()+90</f>
-        <v>45872</v>
+        <v>45888</v>
       </c>
       <c r="BB2" s="15" t="s">
         <v>106</v>
@@ -1482,15 +1483,15 @@
       </c>
       <c r="BF2" s="19">
         <f t="shared" ref="BF2:BF3" si="2">W2</f>
-        <v>45751</v>
+        <v>45767</v>
       </c>
       <c r="BG2" s="19">
         <f t="shared" ref="BG2:BG3" si="3">W2</f>
-        <v>45751</v>
+        <v>45767</v>
       </c>
       <c r="BH2" s="21">
         <f t="shared" ref="BH2:BH3" si="4">AI2</f>
-        <v>46147</v>
+        <v>46163</v>
       </c>
       <c r="BI2" s="28" t="s">
         <v>76</v>
@@ -1500,7 +1501,7 @@
       </c>
       <c r="BK2" s="30">
         <f t="array" ref="BK2:BK3">_xlfn.RANDARRAY(2,1,123456789,999999999,TRUE)</f>
-        <v>202925705</v>
+        <v>661108602</v>
       </c>
       <c r="BL2" s="31" t="s">
         <v>111</v>
@@ -1619,7 +1620,7 @@
       </c>
       <c r="W3" s="21">
         <f t="shared" si="0"/>
-        <v>45751</v>
+        <v>45767</v>
       </c>
       <c r="X3" s="18" t="s">
         <v>87</v>
@@ -1710,7 +1711,7 @@
       </c>
       <c r="BA3" s="19">
         <f t="shared" si="1"/>
-        <v>45872</v>
+        <v>45888</v>
       </c>
       <c r="BB3" s="15" t="s">
         <v>106</v>
@@ -1726,11 +1727,11 @@
       </c>
       <c r="BF3" s="19">
         <f t="shared" si="2"/>
-        <v>45751</v>
+        <v>45767</v>
       </c>
       <c r="BG3" s="19">
         <f t="shared" si="3"/>
-        <v>45751</v>
+        <v>45767</v>
       </c>
       <c r="BH3" s="21">
         <f t="shared" si="4"/>
@@ -1743,7 +1744,7 @@
         <v>110</v>
       </c>
       <c r="BK3" s="30">
-        <v>811320403</v>
+        <v>177289887</v>
       </c>
       <c r="BL3" s="31" t="s">
         <v>135</v>

--- a/Data/Hires/Workday_NewHire_Slovakia_Regression_PK17.xlsx
+++ b/Data/Hires/Workday_NewHire_Slovakia_Regression_PK17.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="1900" yWindow="1900" windowWidth="14400" windowHeight="7360"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420"/>
   </bookViews>
   <sheets>
     <sheet sheetId="1" name="Sheet2" state="visible" r:id="rId4"/>
@@ -235,7 +235,7 @@
     <t>Test1</t>
   </si>
   <si>
-    <t>10699090</t>
+    <t>10699534</t>
   </si>
   <si>
     <t>Passed</t>
@@ -247,10 +247,10 @@
     <t>Slovakia</t>
   </si>
   <si>
-    <t>Einar</t>
-  </si>
-  <si>
-    <t>Metz</t>
+    <t>Franco</t>
+  </si>
+  <si>
+    <t>Botsford</t>
   </si>
   <si>
     <t>041/562 66 84</t>
@@ -383,19 +383,19 @@
     <t>Test2</t>
   </si>
   <si>
-    <t>10699091</t>
+    <t>10699535</t>
   </si>
   <si>
     <t>870 Store Management (Wazup Zudimi (9581610))</t>
   </si>
   <si>
-    <t>Werner</t>
-  </si>
-  <si>
-    <t>Welch</t>
-  </si>
-  <si>
-    <t>Auto 90126088</t>
+    <t>Garnett</t>
+  </si>
+  <si>
+    <t>Powlowski</t>
+  </si>
+  <si>
+    <t>Auto 33031754</t>
   </si>
   <si>
     <t>Permanent</t>
@@ -979,7 +979,8 @@
   <dimension ref="A1:CH3"/>
   <sheetFormatPr defaultRowHeight="15.65" outlineLevelRow="1" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
   <cols>
-    <col min="1" max="2" width="10.81640625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="10.81640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="58.36328125" style="1" customWidth="1"/>
     <col min="3" max="3" width="9.36328125" style="1" customWidth="1"/>
     <col min="4" max="4" width="21.453125" style="1" customWidth="1"/>
     <col min="5" max="5" width="7.54296875" style="1" customWidth="1"/>
@@ -1039,7 +1040,7 @@
     <col min="59" max="59" width="18.26953125" style="1" customWidth="1"/>
     <col min="60" max="60" width="15.08984375" style="1" customWidth="1"/>
     <col min="61" max="61" width="8.453125" style="1" customWidth="1"/>
-    <col min="62" max="62" width="21.7265625" style="1" customWidth="1"/>
+    <col min="62" max="62" width="50.54296875" style="1" customWidth="1"/>
     <col min="63" max="63" width="26.36328125" style="1" customWidth="1"/>
     <col min="64" max="64" width="7" style="1" customWidth="1"/>
     <col min="65" max="65" width="10.7265625" style="1" customWidth="1"/>
@@ -1374,7 +1375,7 @@
       </c>
       <c r="W2" s="21">
         <f t="shared" ref="W2:W3" si="0">TODAY()-31</f>
-        <v>45761</v>
+        <v>45779</v>
       </c>
       <c r="X2" s="18" t="s">
         <v>87</v>
@@ -1411,7 +1412,7 @@
       </c>
       <c r="AI2" s="21">
         <f>TODAY()+365</f>
-        <v>46157</v>
+        <v>46175</v>
       </c>
       <c r="AJ2" s="18" t="s">
         <v>96</v>
@@ -1466,7 +1467,7 @@
       </c>
       <c r="BA2" s="19">
         <f t="shared" ref="BA2:BA3" si="1">TODAY()+90</f>
-        <v>45882</v>
+        <v>45900</v>
       </c>
       <c r="BB2" s="15" t="s">
         <v>106</v>
@@ -1482,15 +1483,15 @@
       </c>
       <c r="BF2" s="19">
         <f t="shared" ref="BF2:BF3" si="2">W2</f>
-        <v>45761</v>
+        <v>45779</v>
       </c>
       <c r="BG2" s="19">
         <f t="shared" ref="BG2:BG3" si="3">W2</f>
-        <v>45761</v>
+        <v>45779</v>
       </c>
       <c r="BH2" s="21">
         <f t="shared" ref="BH2:BH3" si="4">AI2</f>
-        <v>46157</v>
+        <v>46175</v>
       </c>
       <c r="BI2" s="28" t="s">
         <v>76</v>
@@ -1500,7 +1501,7 @@
       </c>
       <c r="BK2" s="30">
         <f t="array" ref="BK2:BK3">_xlfn.RANDARRAY(2,1,123456789,999999999,TRUE)</f>
-        <v>497291593</v>
+        <v>918255176</v>
       </c>
       <c r="BL2" s="31" t="s">
         <v>111</v>
@@ -1619,7 +1620,7 @@
       </c>
       <c r="W3" s="21">
         <f t="shared" si="0"/>
-        <v>45761</v>
+        <v>45779</v>
       </c>
       <c r="X3" s="18" t="s">
         <v>87</v>
@@ -1710,7 +1711,7 @@
       </c>
       <c r="BA3" s="19">
         <f t="shared" si="1"/>
-        <v>45882</v>
+        <v>45900</v>
       </c>
       <c r="BB3" s="15" t="s">
         <v>106</v>
@@ -1726,11 +1727,11 @@
       </c>
       <c r="BF3" s="19">
         <f t="shared" si="2"/>
-        <v>45761</v>
+        <v>45779</v>
       </c>
       <c r="BG3" s="19">
         <f t="shared" si="3"/>
-        <v>45761</v>
+        <v>45779</v>
       </c>
       <c r="BH3" s="21">
         <f t="shared" si="4"/>
@@ -1743,7 +1744,7 @@
         <v>110</v>
       </c>
       <c r="BK3" s="30">
-        <v>392642536</v>
+        <v>768195938</v>
       </c>
       <c r="BL3" s="31" t="s">
         <v>135</v>

--- a/Data/Hires/Workday_NewHire_Slovakia_Regression_PK17.xlsx
+++ b/Data/Hires/Workday_NewHire_Slovakia_Regression_PK17.xlsx
@@ -235,7 +235,7 @@
     <t>Test1</t>
   </si>
   <si>
-    <t>10699534</t>
+    <t>10699678</t>
   </si>
   <si>
     <t>Passed</t>
@@ -247,10 +247,10 @@
     <t>Slovakia</t>
   </si>
   <si>
-    <t>Franco</t>
-  </si>
-  <si>
-    <t>Botsford</t>
+    <t>Napoleon</t>
+  </si>
+  <si>
+    <t>Davis</t>
   </si>
   <si>
     <t>041/562 66 84</t>
@@ -383,19 +383,19 @@
     <t>Test2</t>
   </si>
   <si>
-    <t>10699535</t>
+    <t>10699623</t>
   </si>
   <si>
     <t>870 Store Management (Wazup Zudimi (9581610))</t>
   </si>
   <si>
-    <t>Garnett</t>
-  </si>
-  <si>
-    <t>Powlowski</t>
-  </si>
-  <si>
-    <t>Auto 33031754</t>
+    <t>Peter</t>
+  </si>
+  <si>
+    <t>Wisozk</t>
+  </si>
+  <si>
+    <t>Auto 89162202</t>
   </si>
   <si>
     <t>Permanent</t>
@@ -467,7 +467,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -477,6 +477,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.5999938962981048"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -611,7 +617,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -623,17 +629,20 @@
     <xf numFmtId="49" fontId="2" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
@@ -648,7 +657,7 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -676,7 +685,7 @@
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="1" fontId="2" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
@@ -692,9 +701,6 @@
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1310,489 +1316,489 @@
       <c r="A2" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="D2" s="14" t="s">
+      <c r="D2" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="E2" s="15" t="s">
+      <c r="E2" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="F2" s="16" t="s">
+      <c r="F2" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="G2" s="17" t="s">
+      <c r="G2" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="H2" s="15" t="s">
+      <c r="H2" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="I2" s="18" t="s">
+      <c r="I2" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="J2" s="18" t="s">
+      <c r="J2" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="K2" s="19" t="s">
+      <c r="K2" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="L2" s="15" t="s">
+      <c r="L2" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="M2" s="18" t="s">
+      <c r="M2" s="19" t="s">
         <v>83</v>
       </c>
-      <c r="N2" s="18">
+      <c r="N2" s="19">
         <v>1</v>
       </c>
-      <c r="O2" s="18">
+      <c r="O2" s="19">
         <v>1612</v>
       </c>
-      <c r="P2" s="18">
+      <c r="P2" s="19">
         <v>90851</v>
       </c>
-      <c r="Q2" s="18" t="s">
+      <c r="Q2" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="R2" s="18" t="s">
+      <c r="R2" s="19" t="s">
         <v>76</v>
       </c>
-      <c r="S2" s="18" t="s">
+      <c r="S2" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="T2" s="19" t="s">
+      <c r="T2" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="U2" s="20" t="s">
+      <c r="U2" s="21" t="s">
         <v>86</v>
       </c>
-      <c r="V2" s="18" t="s">
+      <c r="V2" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="W2" s="21">
+      <c r="W2" s="22">
         <f t="shared" ref="W2:W3" si="0">TODAY()-31</f>
-        <v>45779</v>
-      </c>
-      <c r="X2" s="18" t="s">
+        <v>45788</v>
+      </c>
+      <c r="X2" s="19" t="s">
         <v>87</v>
       </c>
-      <c r="Y2" s="22" t="s">
+      <c r="Y2" s="23" t="s">
         <v>88</v>
       </c>
-      <c r="Z2" s="23" t="s">
+      <c r="Z2" s="24" t="s">
         <v>89</v>
       </c>
-      <c r="AA2" s="24" t="s">
+      <c r="AA2" s="25" t="s">
         <v>90</v>
       </c>
-      <c r="AB2" s="19" t="s">
+      <c r="AB2" s="20" t="s">
         <v>91</v>
       </c>
-      <c r="AC2" s="15">
+      <c r="AC2" s="16">
         <v>870</v>
       </c>
-      <c r="AD2" s="15" t="s">
+      <c r="AD2" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="AE2" s="15" t="s">
+      <c r="AE2" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="AF2" s="23" t="s">
+      <c r="AF2" s="24" t="s">
         <v>82</v>
       </c>
-      <c r="AG2" s="15" t="s">
+      <c r="AG2" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="AH2" s="15" t="s">
+      <c r="AH2" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="AI2" s="21">
+      <c r="AI2" s="22">
         <f>TODAY()+365</f>
-        <v>46175</v>
-      </c>
-      <c r="AJ2" s="18" t="s">
+        <v>46184</v>
+      </c>
+      <c r="AJ2" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="AK2" s="25" t="s">
+      <c r="AK2" s="26" t="s">
         <v>97</v>
       </c>
-      <c r="AL2" s="25" t="s">
+      <c r="AL2" s="26" t="s">
         <v>98</v>
       </c>
-      <c r="AM2" s="18" t="s">
+      <c r="AM2" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="AN2" s="18" t="s">
+      <c r="AN2" s="19" t="s">
         <v>100</v>
       </c>
-      <c r="AO2" s="24" t="s">
+      <c r="AO2" s="25" t="s">
         <v>101</v>
       </c>
-      <c r="AP2" s="26" t="s">
+      <c r="AP2" s="27" t="s">
         <v>102</v>
       </c>
-      <c r="AQ2" s="15" t="s">
+      <c r="AQ2" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="AR2" s="19" t="s">
+      <c r="AR2" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="AS2" s="15" t="s">
+      <c r="AS2" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="AT2" s="19" t="s">
+      <c r="AT2" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="AU2" s="19" t="s">
+      <c r="AU2" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="AV2" s="26" t="s">
+      <c r="AV2" s="27" t="s">
         <v>103</v>
       </c>
-      <c r="AW2" s="26" t="s">
+      <c r="AW2" s="27" t="s">
         <v>104</v>
       </c>
-      <c r="AX2" s="27">
+      <c r="AX2" s="28">
         <v>1234567891</v>
       </c>
-      <c r="AY2" s="15" t="s">
+      <c r="AY2" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="AZ2" s="21" t="s">
+      <c r="AZ2" s="22" t="s">
         <v>105</v>
       </c>
-      <c r="BA2" s="19">
+      <c r="BA2" s="20">
         <f t="shared" ref="BA2:BA3" si="1">TODAY()+90</f>
-        <v>45900</v>
-      </c>
-      <c r="BB2" s="15" t="s">
+        <v>45909</v>
+      </c>
+      <c r="BB2" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="BC2" s="18" t="s">
+      <c r="BC2" s="19" t="s">
         <v>107</v>
       </c>
-      <c r="BD2" s="15" t="s">
+      <c r="BD2" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="BE2" s="18" t="s">
+      <c r="BE2" s="19" t="s">
         <v>109</v>
       </c>
-      <c r="BF2" s="19">
+      <c r="BF2" s="20">
         <f t="shared" ref="BF2:BF3" si="2">W2</f>
-        <v>45779</v>
-      </c>
-      <c r="BG2" s="19">
+        <v>45788</v>
+      </c>
+      <c r="BG2" s="20">
         <f t="shared" ref="BG2:BG3" si="3">W2</f>
-        <v>45779</v>
-      </c>
-      <c r="BH2" s="21">
+        <v>45788</v>
+      </c>
+      <c r="BH2" s="22">
         <f t="shared" ref="BH2:BH3" si="4">AI2</f>
-        <v>46175</v>
-      </c>
-      <c r="BI2" s="28" t="s">
+        <v>46184</v>
+      </c>
+      <c r="BI2" s="29" t="s">
         <v>76</v>
       </c>
-      <c r="BJ2" s="29" t="s">
+      <c r="BJ2" s="30" t="s">
         <v>110</v>
       </c>
-      <c r="BK2" s="30">
+      <c r="BK2" s="31">
         <f t="array" ref="BK2:BK3">_xlfn.RANDARRAY(2,1,123456789,999999999,TRUE)</f>
-        <v>918255176</v>
-      </c>
-      <c r="BL2" s="31" t="s">
+        <v>268932618</v>
+      </c>
+      <c r="BL2" s="32" t="s">
         <v>111</v>
       </c>
-      <c r="BM2" s="19" t="s">
+      <c r="BM2" s="20" t="s">
         <v>112</v>
       </c>
-      <c r="BN2" s="28" t="s">
+      <c r="BN2" s="29" t="s">
         <v>113</v>
       </c>
-      <c r="BO2" s="28" t="s">
+      <c r="BO2" s="29" t="s">
         <v>114</v>
       </c>
-      <c r="BP2" s="32" t="s">
+      <c r="BP2" s="33" t="s">
         <v>82</v>
       </c>
-      <c r="BQ2" s="28" t="s">
+      <c r="BQ2" s="29" t="s">
         <v>115</v>
       </c>
-      <c r="BR2" s="28" t="s">
+      <c r="BR2" s="29" t="s">
         <v>76</v>
       </c>
-      <c r="BS2" s="15" t="s">
+      <c r="BS2" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="BT2" s="15" t="s">
+      <c r="BT2" s="16" t="s">
         <v>117</v>
       </c>
-      <c r="BU2" s="28" t="s">
+      <c r="BU2" s="29" t="s">
         <v>118</v>
       </c>
-      <c r="BV2" s="28" t="s">
+      <c r="BV2" s="29" t="s">
         <v>119</v>
       </c>
-      <c r="BW2" s="28" t="s">
+      <c r="BW2" s="29" t="s">
         <v>120</v>
       </c>
-      <c r="BX2" s="33"/>
-      <c r="BY2" s="33"/>
-      <c r="BZ2" s="34"/>
-      <c r="CA2" s="34"/>
-      <c r="CB2" s="33"/>
-      <c r="CC2" s="33"/>
-      <c r="CD2" s="33"/>
-      <c r="CE2" s="33"/>
-      <c r="CF2" s="33"/>
-      <c r="CG2" s="33"/>
-      <c r="CH2" s="33"/>
+      <c r="BX2" s="34"/>
+      <c r="BY2" s="34"/>
+      <c r="BZ2" s="35"/>
+      <c r="CA2" s="35"/>
+      <c r="CB2" s="34"/>
+      <c r="CC2" s="34"/>
+      <c r="CD2" s="34"/>
+      <c r="CE2" s="34"/>
+      <c r="CF2" s="34"/>
+      <c r="CG2" s="34"/>
+      <c r="CH2" s="34"/>
     </row>
     <row r="3" ht="15.65" customHeight="1" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="B3" s="35" t="s">
+      <c r="B3" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="D3" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="E3" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="F3" s="16" t="s">
+      <c r="F3" s="17" t="s">
         <v>124</v>
       </c>
-      <c r="G3" s="17" t="s">
+      <c r="G3" s="18" t="s">
         <v>125</v>
       </c>
-      <c r="H3" s="15" t="s">
+      <c r="H3" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="I3" s="18" t="s">
+      <c r="I3" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="J3" s="18" t="s">
+      <c r="J3" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="K3" s="19" t="s">
+      <c r="K3" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="L3" s="15" t="s">
+      <c r="L3" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="M3" s="18" t="s">
+      <c r="M3" s="19" t="s">
         <v>83</v>
       </c>
-      <c r="N3" s="18">
+      <c r="N3" s="19">
         <v>1</v>
       </c>
-      <c r="O3" s="18">
+      <c r="O3" s="19">
         <v>1612</v>
       </c>
-      <c r="P3" s="18">
+      <c r="P3" s="19">
         <v>90851</v>
       </c>
-      <c r="Q3" s="18" t="s">
+      <c r="Q3" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="R3" s="18" t="s">
+      <c r="R3" s="19" t="s">
         <v>76</v>
       </c>
-      <c r="S3" s="18" t="s">
+      <c r="S3" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="T3" s="19" t="s">
+      <c r="T3" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="U3" s="20" t="s">
+      <c r="U3" s="21" t="s">
         <v>86</v>
       </c>
-      <c r="V3" s="18" t="s">
+      <c r="V3" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="W3" s="21">
+      <c r="W3" s="22">
         <f t="shared" si="0"/>
-        <v>45779</v>
-      </c>
-      <c r="X3" s="18" t="s">
+        <v>45788</v>
+      </c>
+      <c r="X3" s="19" t="s">
         <v>87</v>
       </c>
-      <c r="Y3" s="22" t="s">
+      <c r="Y3" s="23" t="s">
         <v>126</v>
       </c>
-      <c r="Z3" s="15" t="s">
+      <c r="Z3" s="16" t="s">
         <v>127</v>
       </c>
-      <c r="AA3" s="24" t="s">
+      <c r="AA3" s="25" t="s">
         <v>128</v>
       </c>
-      <c r="AB3" s="19" t="s">
+      <c r="AB3" s="20" t="s">
         <v>91</v>
       </c>
-      <c r="AC3" s="15" t="s">
+      <c r="AC3" s="16" t="s">
         <v>129</v>
       </c>
-      <c r="AD3" s="15" t="s">
+      <c r="AD3" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="AE3" s="15">
+      <c r="AE3" s="16">
         <v>40</v>
       </c>
-      <c r="AF3" s="23">
+      <c r="AF3" s="24">
         <v>40</v>
       </c>
-      <c r="AG3" s="15" t="s">
+      <c r="AG3" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="AH3" s="15" t="s">
+      <c r="AH3" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="AI3" s="21" t="s">
+      <c r="AI3" s="22" t="s">
         <v>82</v>
       </c>
-      <c r="AJ3" s="18" t="s">
+      <c r="AJ3" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="AK3" s="25" t="s">
+      <c r="AK3" s="26" t="s">
         <v>130</v>
       </c>
-      <c r="AL3" s="25" t="s">
+      <c r="AL3" s="26" t="s">
         <v>131</v>
       </c>
-      <c r="AM3" s="18" t="s">
+      <c r="AM3" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="AN3" s="18" t="s">
+      <c r="AN3" s="19" t="s">
         <v>100</v>
       </c>
-      <c r="AO3" s="24" t="s">
+      <c r="AO3" s="25" t="s">
         <v>132</v>
       </c>
-      <c r="AP3" s="26" t="s">
+      <c r="AP3" s="27" t="s">
         <v>133</v>
       </c>
-      <c r="AQ3" s="15" t="s">
+      <c r="AQ3" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="AR3" s="19" t="s">
+      <c r="AR3" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="AS3" s="15" t="s">
+      <c r="AS3" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="AT3" s="19" t="s">
+      <c r="AT3" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="AU3" s="19" t="s">
+      <c r="AU3" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="AV3" s="26" t="s">
+      <c r="AV3" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="AW3" s="26" t="s">
+      <c r="AW3" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="AX3" s="26" t="s">
+      <c r="AX3" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="AY3" s="15" t="s">
+      <c r="AY3" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="AZ3" s="21" t="s">
+      <c r="AZ3" s="22" t="s">
         <v>82</v>
       </c>
-      <c r="BA3" s="19">
+      <c r="BA3" s="20">
         <f t="shared" si="1"/>
-        <v>45900</v>
-      </c>
-      <c r="BB3" s="15" t="s">
+        <v>45909</v>
+      </c>
+      <c r="BB3" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="BC3" s="18" t="s">
+      <c r="BC3" s="19" t="s">
         <v>107</v>
       </c>
-      <c r="BD3" s="15" t="s">
+      <c r="BD3" s="16" t="s">
         <v>134</v>
       </c>
-      <c r="BE3" s="18" t="s">
+      <c r="BE3" s="19" t="s">
         <v>109</v>
       </c>
-      <c r="BF3" s="19">
+      <c r="BF3" s="20">
         <f t="shared" si="2"/>
-        <v>45779</v>
-      </c>
-      <c r="BG3" s="19">
+        <v>45788</v>
+      </c>
+      <c r="BG3" s="20">
         <f t="shared" si="3"/>
-        <v>45779</v>
-      </c>
-      <c r="BH3" s="21">
+        <v>45788</v>
+      </c>
+      <c r="BH3" s="22">
         <f t="shared" si="4"/>
         <v>NaN</v>
       </c>
-      <c r="BI3" s="28" t="s">
+      <c r="BI3" s="29" t="s">
         <v>76</v>
       </c>
-      <c r="BJ3" s="29" t="s">
+      <c r="BJ3" s="30" t="s">
         <v>110</v>
       </c>
-      <c r="BK3" s="30">
-        <v>768195938</v>
-      </c>
-      <c r="BL3" s="31" t="s">
+      <c r="BK3" s="31">
+        <v>443734695</v>
+      </c>
+      <c r="BL3" s="32" t="s">
         <v>135</v>
       </c>
-      <c r="BM3" s="19" t="s">
+      <c r="BM3" s="20" t="s">
         <v>112</v>
       </c>
-      <c r="BN3" s="28" t="s">
+      <c r="BN3" s="29" t="s">
         <v>113</v>
       </c>
-      <c r="BO3" s="28" t="s">
+      <c r="BO3" s="29" t="s">
         <v>114</v>
       </c>
-      <c r="BP3" s="32" t="s">
+      <c r="BP3" s="33" t="s">
         <v>82</v>
       </c>
-      <c r="BQ3" s="28" t="s">
+      <c r="BQ3" s="29" t="s">
         <v>115</v>
       </c>
-      <c r="BR3" s="28" t="s">
+      <c r="BR3" s="29" t="s">
         <v>76</v>
       </c>
-      <c r="BS3" s="15" t="s">
+      <c r="BS3" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="BT3" s="15" t="s">
+      <c r="BT3" s="16" t="s">
         <v>117</v>
       </c>
-      <c r="BU3" s="28" t="s">
+      <c r="BU3" s="29" t="s">
         <v>118</v>
       </c>
-      <c r="BV3" s="28" t="s">
+      <c r="BV3" s="29" t="s">
         <v>119</v>
       </c>
-      <c r="BW3" s="28" t="s">
+      <c r="BW3" s="29" t="s">
         <v>120</v>
       </c>
-      <c r="BX3" s="33"/>
-      <c r="BY3" s="33"/>
-      <c r="BZ3" s="34"/>
-      <c r="CA3" s="34"/>
-      <c r="CB3" s="33"/>
-      <c r="CC3" s="33"/>
-      <c r="CD3" s="33"/>
-      <c r="CE3" s="33"/>
-      <c r="CF3" s="33"/>
-      <c r="CG3" s="33"/>
-      <c r="CH3" s="33"/>
+      <c r="BX3" s="34"/>
+      <c r="BY3" s="34"/>
+      <c r="BZ3" s="35"/>
+      <c r="CA3" s="35"/>
+      <c r="CB3" s="34"/>
+      <c r="CC3" s="34"/>
+      <c r="CD3" s="34"/>
+      <c r="CE3" s="34"/>
+      <c r="CF3" s="34"/>
+      <c r="CG3" s="34"/>
+      <c r="CH3" s="34"/>
     </row>
   </sheetData>
   <dataValidations count="7">

--- a/Data/Hires/Workday_NewHire_Slovakia_Regression_PK17.xlsx
+++ b/Data/Hires/Workday_NewHire_Slovakia_Regression_PK17.xlsx
@@ -1,20 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{4715BC09-F8B0-4900-88B1-1DD6DAA1149E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1900" yWindow="1900" windowWidth="14400" windowHeight="7360"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Sheet2" state="visible" r:id="rId4"/>
+    <sheet name="Sheet2" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="131">
   <si>
     <t>TestCaseIDs</t>
   </si>
@@ -235,24 +250,12 @@
     <t>Test1</t>
   </si>
   <si>
-    <t>10699090</t>
-  </si>
-  <si>
-    <t>Passed</t>
-  </si>
-  <si>
     <t>870 Recruitment (Wazup Zudimi (9581610))</t>
   </si>
   <si>
     <t>Slovakia</t>
   </si>
   <si>
-    <t>Einar</t>
-  </si>
-  <si>
-    <t>Metz</t>
-  </si>
-  <si>
     <t>041/562 66 84</t>
   </si>
   <si>
@@ -319,7 +322,7 @@
     <t>SK Monthly</t>
   </si>
   <si>
-    <t xml:space="preserve">Meal Voucher Card </t>
+    <t>Meal Voucher Card </t>
   </si>
   <si>
     <t>Všeobecná zdrav. Poisť.</t>
@@ -383,19 +386,10 @@
     <t>Test2</t>
   </si>
   <si>
-    <t>10699091</t>
-  </si>
-  <si>
     <t>870 Store Management (Wazup Zudimi (9581610))</t>
   </si>
   <si>
-    <t>Werner</t>
-  </si>
-  <si>
-    <t>Welch</t>
-  </si>
-  <si>
-    <t>Auto 90126088</t>
+    <t>Auto 30165015</t>
   </si>
   <si>
     <t>Permanent</t>
@@ -423,51 +417,57 @@
   </si>
   <si>
     <t>Female</t>
+  </si>
+  <si>
+    <t>Auto 89024414</t>
+  </si>
+  <si>
+    <t>Auto 19951165</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <color rgb="FFFF0000"/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <family val="2"/>
-      <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <color theme="1"/>
-      <family val="2"/>
-      <sz val="14"/>
-      <name val="Arial"/>
     </font>
     <font>
       <u/>
+      <sz val="11"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -476,18 +476,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.5999938962981048"/>
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00FF00"/>
+        <fgColor rgb="FFFF0000"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.7999816888943144"/>
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -507,17 +513,27 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -527,15 +543,25 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin"/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -546,7 +572,9 @@
         <color indexed="64"/>
       </right>
       <top/>
-      <bottom style="thin"/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -556,38 +584,56 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin"/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
       <top/>
-      <bottom style="thin"/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -694,6 +740,12 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -975,9 +1027,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:CH3"/>
-  <sheetFormatPr defaultRowHeight="15.65" outlineLevelRow="1" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:CH7"/>
+  <sheetFormatPr defaultRowHeight="15.65" customHeight="1" outlineLevelRow="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="10.81640625" style="1" customWidth="1"/>
     <col min="3" max="3" width="9.36328125" style="1" customWidth="1"/>
@@ -1067,7 +1119,7 @@
     <col min="87" max="87" width="8.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.5" customHeight="1" spans="1:86" s="3" customFormat="1" x14ac:dyDescent="0.25" outlineLevel="1" collapsed="1">
+    <row r="1" spans="1:86" s="3" customFormat="1" ht="14.5" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1305,45 +1357,37 @@
       <c r="CG1" s="11"/>
       <c r="CH1" s="12"/>
     </row>
-    <row r="2" ht="15.65" customHeight="1" spans="1:86" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:86" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="36"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="C2" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="D2" s="14" t="s">
+      <c r="E2" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="F2" s="16"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="E2" s="15" t="s">
+      <c r="I2" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="F2" s="16" t="s">
+      <c r="J2" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="G2" s="17" t="s">
-        <v>78</v>
-      </c>
-      <c r="H2" s="15" t="s">
+      <c r="K2" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="L2" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="M2" s="18" t="s">
         <v>79</v>
-      </c>
-      <c r="I2" s="18" t="s">
-        <v>80</v>
-      </c>
-      <c r="J2" s="18" t="s">
-        <v>81</v>
-      </c>
-      <c r="K2" s="19" t="s">
-        <v>82</v>
-      </c>
-      <c r="L2" s="15" t="s">
-        <v>76</v>
-      </c>
-      <c r="M2" s="18" t="s">
-        <v>83</v>
       </c>
       <c r="N2" s="18">
         <v>1</v>
@@ -1355,188 +1399,188 @@
         <v>90851</v>
       </c>
       <c r="Q2" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="R2" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="S2" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="T2" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="U2" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="V2" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="W2" s="21">
+        <f t="shared" ref="W2:W7" ca="1" si="0">TODAY()-31</f>
+        <v>45794</v>
+      </c>
+      <c r="X2" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="Y2" s="22" t="s">
         <v>84</v>
       </c>
-      <c r="R2" s="18" t="s">
-        <v>76</v>
-      </c>
-      <c r="S2" s="18" t="s">
-        <v>81</v>
-      </c>
-      <c r="T2" s="19" t="s">
+      <c r="Z2" s="23" t="s">
         <v>85</v>
       </c>
-      <c r="U2" s="20" t="s">
+      <c r="AA2" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="V2" s="18" t="s">
-        <v>81</v>
-      </c>
-      <c r="W2" s="21">
-        <f t="shared" ref="W2:W3" si="0">TODAY()-31</f>
-        <v>45761</v>
-      </c>
-      <c r="X2" s="18" t="s">
+      <c r="AB2" s="19" t="s">
         <v>87</v>
-      </c>
-      <c r="Y2" s="22" t="s">
-        <v>88</v>
-      </c>
-      <c r="Z2" s="23" t="s">
-        <v>89</v>
-      </c>
-      <c r="AA2" s="24" t="s">
-        <v>90</v>
-      </c>
-      <c r="AB2" s="19" t="s">
-        <v>91</v>
       </c>
       <c r="AC2" s="15">
         <v>870</v>
       </c>
       <c r="AD2" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="AE2" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="AF2" s="23" t="s">
+        <v>78</v>
+      </c>
+      <c r="AG2" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="AH2" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="AI2" s="21">
+        <f ca="1">TODAY()+365</f>
+        <v>46190</v>
+      </c>
+      <c r="AJ2" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="AE2" s="15" t="s">
+      <c r="AK2" s="25" t="s">
         <v>93</v>
       </c>
-      <c r="AF2" s="23" t="s">
-        <v>82</v>
-      </c>
-      <c r="AG2" s="15" t="s">
+      <c r="AL2" s="25" t="s">
         <v>94</v>
       </c>
-      <c r="AH2" s="15" t="s">
+      <c r="AM2" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="AI2" s="21">
-        <f>TODAY()+365</f>
-        <v>46157</v>
-      </c>
-      <c r="AJ2" s="18" t="s">
+      <c r="AN2" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="AK2" s="25" t="s">
+      <c r="AO2" s="24" t="s">
         <v>97</v>
       </c>
-      <c r="AL2" s="25" t="s">
+      <c r="AP2" s="26" t="s">
         <v>98</v>
       </c>
-      <c r="AM2" s="18" t="s">
+      <c r="AQ2" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="AR2" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="AS2" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="AT2" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="AU2" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="AV2" s="26" t="s">
         <v>99</v>
       </c>
-      <c r="AN2" s="18" t="s">
+      <c r="AW2" s="26" t="s">
         <v>100</v>
-      </c>
-      <c r="AO2" s="24" t="s">
-        <v>101</v>
-      </c>
-      <c r="AP2" s="26" t="s">
-        <v>102</v>
-      </c>
-      <c r="AQ2" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="AR2" s="19" t="s">
-        <v>82</v>
-      </c>
-      <c r="AS2" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="AT2" s="19" t="s">
-        <v>82</v>
-      </c>
-      <c r="AU2" s="19" t="s">
-        <v>82</v>
-      </c>
-      <c r="AV2" s="26" t="s">
-        <v>103</v>
-      </c>
-      <c r="AW2" s="26" t="s">
-        <v>104</v>
       </c>
       <c r="AX2" s="27">
         <v>1234567891</v>
       </c>
       <c r="AY2" s="15" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="AZ2" s="21" t="s">
+        <v>101</v>
+      </c>
+      <c r="BA2" s="19">
+        <f t="shared" ref="BA2:BA7" ca="1" si="1">TODAY()+90</f>
+        <v>45915</v>
+      </c>
+      <c r="BB2" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="BC2" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="BD2" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="BE2" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="BA2" s="19">
-        <f t="shared" ref="BA2:BA3" si="1">TODAY()+90</f>
-        <v>45882</v>
-      </c>
-      <c r="BB2" s="15" t="s">
+      <c r="BF2" s="19">
+        <f t="shared" ref="BF2:BF3" ca="1" si="2">W2</f>
+        <v>45794</v>
+      </c>
+      <c r="BG2" s="19">
+        <f t="shared" ref="BG2:BG3" ca="1" si="3">W2</f>
+        <v>45794</v>
+      </c>
+      <c r="BH2" s="21">
+        <f t="shared" ref="BH2:BH3" ca="1" si="4">AI2</f>
+        <v>46190</v>
+      </c>
+      <c r="BI2" s="28" t="s">
+        <v>74</v>
+      </c>
+      <c r="BJ2" s="29" t="s">
         <v>106</v>
       </c>
-      <c r="BC2" s="18" t="s">
+      <c r="BK2" s="30">
+        <f t="array" aca="1" ref="BK2:BK3" ca="1">_xlfn.RANDARRAY(2,1,123456789,999999999,TRUE)</f>
+        <v>571268906</v>
+      </c>
+      <c r="BL2" s="31" t="s">
         <v>107</v>
       </c>
-      <c r="BD2" s="15" t="s">
+      <c r="BM2" s="19" t="s">
         <v>108</v>
       </c>
-      <c r="BE2" s="18" t="s">
+      <c r="BN2" s="28" t="s">
         <v>109</v>
       </c>
-      <c r="BF2" s="19">
-        <f t="shared" ref="BF2:BF3" si="2">W2</f>
-        <v>45761</v>
-      </c>
-      <c r="BG2" s="19">
-        <f t="shared" ref="BG2:BG3" si="3">W2</f>
-        <v>45761</v>
-      </c>
-      <c r="BH2" s="21">
-        <f t="shared" ref="BH2:BH3" si="4">AI2</f>
-        <v>46157</v>
-      </c>
-      <c r="BI2" s="28" t="s">
-        <v>76</v>
-      </c>
-      <c r="BJ2" s="29" t="s">
+      <c r="BO2" s="28" t="s">
         <v>110</v>
       </c>
-      <c r="BK2" s="30">
-        <f t="array" ref="BK2:BK3">_xlfn.RANDARRAY(2,1,123456789,999999999,TRUE)</f>
-        <v>497291593</v>
-      </c>
-      <c r="BL2" s="31" t="s">
+      <c r="BP2" s="32" t="s">
+        <v>78</v>
+      </c>
+      <c r="BQ2" s="28" t="s">
         <v>111</v>
       </c>
-      <c r="BM2" s="19" t="s">
+      <c r="BR2" s="28" t="s">
+        <v>74</v>
+      </c>
+      <c r="BS2" s="15" t="s">
         <v>112</v>
       </c>
-      <c r="BN2" s="28" t="s">
+      <c r="BT2" s="15" t="s">
         <v>113</v>
       </c>
-      <c r="BO2" s="28" t="s">
+      <c r="BU2" s="28" t="s">
         <v>114</v>
       </c>
-      <c r="BP2" s="32" t="s">
-        <v>82</v>
-      </c>
-      <c r="BQ2" s="28" t="s">
+      <c r="BV2" s="28" t="s">
         <v>115</v>
       </c>
-      <c r="BR2" s="28" t="s">
-        <v>76</v>
-      </c>
-      <c r="BS2" s="15" t="s">
+      <c r="BW2" s="28" t="s">
         <v>116</v>
-      </c>
-      <c r="BT2" s="15" t="s">
-        <v>117</v>
-      </c>
-      <c r="BU2" s="28" t="s">
-        <v>118</v>
-      </c>
-      <c r="BV2" s="28" t="s">
-        <v>119</v>
-      </c>
-      <c r="BW2" s="28" t="s">
-        <v>120</v>
       </c>
       <c r="BX2" s="33"/>
       <c r="BY2" s="33"/>
@@ -1550,45 +1594,37 @@
       <c r="CG2" s="33"/>
       <c r="CH2" s="33"/>
     </row>
-    <row r="3" ht="15.65" customHeight="1" spans="1:86" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:86" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="B3" s="35" t="s">
-        <v>122</v>
-      </c>
-      <c r="C3" s="13" t="s">
-        <v>74</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="B3" s="37"/>
+      <c r="C3" s="13"/>
       <c r="D3" s="14" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="E3" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="F3" s="16"/>
+      <c r="G3" s="17"/>
+      <c r="H3" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="I3" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="F3" s="16" t="s">
-        <v>124</v>
-      </c>
-      <c r="G3" s="17" t="s">
-        <v>125</v>
-      </c>
-      <c r="H3" s="15" t="s">
+      <c r="J3" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="K3" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="L3" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="M3" s="18" t="s">
         <v>79</v>
-      </c>
-      <c r="I3" s="18" t="s">
-        <v>80</v>
-      </c>
-      <c r="J3" s="18" t="s">
-        <v>81</v>
-      </c>
-      <c r="K3" s="19" t="s">
-        <v>82</v>
-      </c>
-      <c r="L3" s="15" t="s">
-        <v>76</v>
-      </c>
-      <c r="M3" s="18" t="s">
-        <v>83</v>
       </c>
       <c r="N3" s="18">
         <v>1</v>
@@ -1600,47 +1636,47 @@
         <v>90851</v>
       </c>
       <c r="Q3" s="18" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="R3" s="18" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="S3" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="T3" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="T3" s="19" t="s">
-        <v>85</v>
-      </c>
       <c r="U3" s="20" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="V3" s="18" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="W3" s="21">
-        <f t="shared" si="0"/>
-        <v>45761</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>45794</v>
       </c>
       <c r="X3" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="Y3" s="22" t="s">
+        <v>119</v>
+      </c>
+      <c r="Z3" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="AA3" s="24" t="s">
+        <v>121</v>
+      </c>
+      <c r="AB3" s="19" t="s">
         <v>87</v>
       </c>
-      <c r="Y3" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="Z3" s="15" t="s">
-        <v>127</v>
-      </c>
-      <c r="AA3" s="24" t="s">
-        <v>128</v>
-      </c>
-      <c r="AB3" s="19" t="s">
-        <v>91</v>
-      </c>
       <c r="AC3" s="15" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="AD3" s="15" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="AE3" s="15">
         <v>40</v>
@@ -1649,137 +1685,138 @@
         <v>40</v>
       </c>
       <c r="AG3" s="15" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="AH3" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="AI3" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="AJ3" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="AK3" s="25" t="s">
+        <v>123</v>
+      </c>
+      <c r="AL3" s="25" t="s">
+        <v>124</v>
+      </c>
+      <c r="AM3" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="AI3" s="21" t="s">
-        <v>82</v>
-      </c>
-      <c r="AJ3" s="18" t="s">
+      <c r="AN3" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="AK3" s="25" t="s">
-        <v>130</v>
-      </c>
-      <c r="AL3" s="25" t="s">
-        <v>131</v>
-      </c>
-      <c r="AM3" s="18" t="s">
-        <v>99</v>
-      </c>
-      <c r="AN3" s="18" t="s">
-        <v>100</v>
-      </c>
       <c r="AO3" s="24" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="AP3" s="26" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="AQ3" s="15" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="AR3" s="19" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="AS3" s="15" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="AT3" s="19" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="AU3" s="19" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="AV3" s="26" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="AW3" s="26" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="AX3" s="26" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="AY3" s="15" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="AZ3" s="21" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="BA3" s="19">
-        <f t="shared" si="1"/>
-        <v>45882</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>45915</v>
       </c>
       <c r="BB3" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="BC3" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="BD3" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="BE3" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="BF3" s="19">
+        <f t="shared" ca="1" si="2"/>
+        <v>45794</v>
+      </c>
+      <c r="BG3" s="19">
+        <f t="shared" ca="1" si="3"/>
+        <v>45794</v>
+      </c>
+      <c r="BH3" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v>N/A</v>
+      </c>
+      <c r="BI3" s="28" t="s">
+        <v>74</v>
+      </c>
+      <c r="BJ3" s="29" t="s">
         <v>106</v>
       </c>
-      <c r="BC3" s="18" t="s">
-        <v>107</v>
-      </c>
-      <c r="BD3" s="15" t="s">
-        <v>134</v>
-      </c>
-      <c r="BE3" s="18" t="s">
+      <c r="BK3" s="30">
+        <f ca="1"/>
+        <v>427497548</v>
+      </c>
+      <c r="BL3" s="31" t="s">
+        <v>128</v>
+      </c>
+      <c r="BM3" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="BN3" s="28" t="s">
         <v>109</v>
       </c>
-      <c r="BF3" s="19">
-        <f t="shared" si="2"/>
-        <v>45761</v>
-      </c>
-      <c r="BG3" s="19">
-        <f t="shared" si="3"/>
-        <v>45761</v>
-      </c>
-      <c r="BH3" s="21">
-        <f t="shared" si="4"/>
-        <v>NaN</v>
-      </c>
-      <c r="BI3" s="28" t="s">
-        <v>76</v>
-      </c>
-      <c r="BJ3" s="29" t="s">
+      <c r="BO3" s="28" t="s">
         <v>110</v>
       </c>
-      <c r="BK3" s="30">
-        <v>392642536</v>
-      </c>
-      <c r="BL3" s="31" t="s">
-        <v>135</v>
-      </c>
-      <c r="BM3" s="19" t="s">
+      <c r="BP3" s="32" t="s">
+        <v>78</v>
+      </c>
+      <c r="BQ3" s="28" t="s">
+        <v>111</v>
+      </c>
+      <c r="BR3" s="28" t="s">
+        <v>74</v>
+      </c>
+      <c r="BS3" s="15" t="s">
         <v>112</v>
       </c>
-      <c r="BN3" s="28" t="s">
+      <c r="BT3" s="15" t="s">
         <v>113</v>
       </c>
-      <c r="BO3" s="28" t="s">
+      <c r="BU3" s="28" t="s">
         <v>114</v>
       </c>
-      <c r="BP3" s="32" t="s">
-        <v>82</v>
-      </c>
-      <c r="BQ3" s="28" t="s">
+      <c r="BV3" s="28" t="s">
         <v>115</v>
       </c>
-      <c r="BR3" s="28" t="s">
-        <v>76</v>
-      </c>
-      <c r="BS3" s="15" t="s">
+      <c r="BW3" s="28" t="s">
         <v>116</v>
-      </c>
-      <c r="BT3" s="15" t="s">
-        <v>117</v>
-      </c>
-      <c r="BU3" s="28" t="s">
-        <v>118</v>
-      </c>
-      <c r="BV3" s="28" t="s">
-        <v>119</v>
-      </c>
-      <c r="BW3" s="28" t="s">
-        <v>120</v>
       </c>
       <c r="BX3" s="33"/>
       <c r="BY3" s="33"/>
@@ -1793,36 +1830,968 @@
       <c r="CG3" s="33"/>
       <c r="CH3" s="33"/>
     </row>
+    <row r="4" spans="1:86" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B4" s="36"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="F4" s="16"/>
+      <c r="G4" s="17"/>
+      <c r="H4" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="I4" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="J4" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="K4" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="L4" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="M4" s="18" t="s">
+        <v>79</v>
+      </c>
+      <c r="N4" s="18">
+        <v>1</v>
+      </c>
+      <c r="O4" s="18">
+        <v>1612</v>
+      </c>
+      <c r="P4" s="18">
+        <v>90851</v>
+      </c>
+      <c r="Q4" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="R4" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="S4" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="T4" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="U4" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="V4" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="W4" s="21">
+        <f t="shared" ca="1" si="0"/>
+        <v>45794</v>
+      </c>
+      <c r="X4" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="Y4" s="22" t="s">
+        <v>84</v>
+      </c>
+      <c r="Z4" s="23" t="s">
+        <v>85</v>
+      </c>
+      <c r="AA4" s="24" t="s">
+        <v>86</v>
+      </c>
+      <c r="AB4" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="AC4" s="15">
+        <v>870</v>
+      </c>
+      <c r="AD4" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="AE4" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="AF4" s="23" t="s">
+        <v>78</v>
+      </c>
+      <c r="AG4" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="AH4" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="AI4" s="21">
+        <f ca="1">TODAY()+365</f>
+        <v>46190</v>
+      </c>
+      <c r="AJ4" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="AK4" s="25" t="s">
+        <v>93</v>
+      </c>
+      <c r="AL4" s="25" t="s">
+        <v>94</v>
+      </c>
+      <c r="AM4" s="18" t="s">
+        <v>95</v>
+      </c>
+      <c r="AN4" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="AO4" s="24" t="s">
+        <v>97</v>
+      </c>
+      <c r="AP4" s="26" t="s">
+        <v>98</v>
+      </c>
+      <c r="AQ4" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="AR4" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="AS4" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="AT4" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="AU4" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="AV4" s="26" t="s">
+        <v>99</v>
+      </c>
+      <c r="AW4" s="26" t="s">
+        <v>100</v>
+      </c>
+      <c r="AX4" s="27">
+        <v>1234567891</v>
+      </c>
+      <c r="AY4" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="AZ4" s="21" t="s">
+        <v>101</v>
+      </c>
+      <c r="BA4" s="19">
+        <f t="shared" ca="1" si="1"/>
+        <v>45915</v>
+      </c>
+      <c r="BB4" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="BC4" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="BD4" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="BE4" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="BF4" s="19">
+        <f t="shared" ref="BF4:BF7" ca="1" si="5">W4</f>
+        <v>45794</v>
+      </c>
+      <c r="BG4" s="19">
+        <f t="shared" ref="BG4:BG7" ca="1" si="6">W4</f>
+        <v>45794</v>
+      </c>
+      <c r="BH4" s="21">
+        <f t="shared" ref="BH4:BH7" ca="1" si="7">AI4</f>
+        <v>46190</v>
+      </c>
+      <c r="BI4" s="28" t="s">
+        <v>74</v>
+      </c>
+      <c r="BJ4" s="29" t="s">
+        <v>106</v>
+      </c>
+      <c r="BK4" s="30">
+        <f t="array" aca="1" ref="BK4:BK5" ca="1">_xlfn.RANDARRAY(2,1,123456789,999999999,TRUE)</f>
+        <v>770708346</v>
+      </c>
+      <c r="BL4" s="31" t="s">
+        <v>107</v>
+      </c>
+      <c r="BM4" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="BN4" s="28" t="s">
+        <v>109</v>
+      </c>
+      <c r="BO4" s="28" t="s">
+        <v>110</v>
+      </c>
+      <c r="BP4" s="32" t="s">
+        <v>78</v>
+      </c>
+      <c r="BQ4" s="28" t="s">
+        <v>111</v>
+      </c>
+      <c r="BR4" s="28" t="s">
+        <v>74</v>
+      </c>
+      <c r="BS4" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="BT4" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="BU4" s="28" t="s">
+        <v>114</v>
+      </c>
+      <c r="BV4" s="28" t="s">
+        <v>115</v>
+      </c>
+      <c r="BW4" s="28" t="s">
+        <v>116</v>
+      </c>
+      <c r="BX4" s="33"/>
+      <c r="BY4" s="33"/>
+      <c r="BZ4" s="34"/>
+      <c r="CA4" s="34"/>
+      <c r="CB4" s="33"/>
+      <c r="CC4" s="33"/>
+      <c r="CD4" s="33"/>
+      <c r="CE4" s="33"/>
+      <c r="CF4" s="33"/>
+      <c r="CG4" s="33"/>
+      <c r="CH4" s="33"/>
+    </row>
+    <row r="5" spans="1:86" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B5" s="35"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="F5" s="16"/>
+      <c r="G5" s="17"/>
+      <c r="H5" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="I5" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="J5" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="K5" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="L5" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="M5" s="18" t="s">
+        <v>79</v>
+      </c>
+      <c r="N5" s="18">
+        <v>1</v>
+      </c>
+      <c r="O5" s="18">
+        <v>1612</v>
+      </c>
+      <c r="P5" s="18">
+        <v>90851</v>
+      </c>
+      <c r="Q5" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="R5" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="S5" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="T5" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="U5" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="V5" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="W5" s="21">
+        <f t="shared" ca="1" si="0"/>
+        <v>45794</v>
+      </c>
+      <c r="X5" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="Y5" s="22" t="s">
+        <v>129</v>
+      </c>
+      <c r="Z5" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="AA5" s="24" t="s">
+        <v>121</v>
+      </c>
+      <c r="AB5" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="AC5" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="AD5" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="AE5" s="15">
+        <v>40</v>
+      </c>
+      <c r="AF5" s="23">
+        <v>40</v>
+      </c>
+      <c r="AG5" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="AH5" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="AI5" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="AJ5" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="AK5" s="25" t="s">
+        <v>123</v>
+      </c>
+      <c r="AL5" s="25" t="s">
+        <v>124</v>
+      </c>
+      <c r="AM5" s="18" t="s">
+        <v>95</v>
+      </c>
+      <c r="AN5" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="AO5" s="24" t="s">
+        <v>125</v>
+      </c>
+      <c r="AP5" s="26" t="s">
+        <v>126</v>
+      </c>
+      <c r="AQ5" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="AR5" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="AS5" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="AT5" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="AU5" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="AV5" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="AW5" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="AX5" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="AY5" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="AZ5" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="BA5" s="19">
+        <f t="shared" ca="1" si="1"/>
+        <v>45915</v>
+      </c>
+      <c r="BB5" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="BC5" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="BD5" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="BE5" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="BF5" s="19">
+        <f t="shared" ca="1" si="5"/>
+        <v>45794</v>
+      </c>
+      <c r="BG5" s="19">
+        <f t="shared" ca="1" si="6"/>
+        <v>45794</v>
+      </c>
+      <c r="BH5" s="21" t="str">
+        <f t="shared" si="7"/>
+        <v>N/A</v>
+      </c>
+      <c r="BI5" s="28" t="s">
+        <v>74</v>
+      </c>
+      <c r="BJ5" s="29" t="s">
+        <v>106</v>
+      </c>
+      <c r="BK5" s="30">
+        <f ca="1"/>
+        <v>257672960</v>
+      </c>
+      <c r="BL5" s="31" t="s">
+        <v>128</v>
+      </c>
+      <c r="BM5" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="BN5" s="28" t="s">
+        <v>109</v>
+      </c>
+      <c r="BO5" s="28" t="s">
+        <v>110</v>
+      </c>
+      <c r="BP5" s="32" t="s">
+        <v>78</v>
+      </c>
+      <c r="BQ5" s="28" t="s">
+        <v>111</v>
+      </c>
+      <c r="BR5" s="28" t="s">
+        <v>74</v>
+      </c>
+      <c r="BS5" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="BT5" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="BU5" s="28" t="s">
+        <v>114</v>
+      </c>
+      <c r="BV5" s="28" t="s">
+        <v>115</v>
+      </c>
+      <c r="BW5" s="28" t="s">
+        <v>116</v>
+      </c>
+      <c r="BX5" s="33"/>
+      <c r="BY5" s="33"/>
+      <c r="BZ5" s="34"/>
+      <c r="CA5" s="34"/>
+      <c r="CB5" s="33"/>
+      <c r="CC5" s="33"/>
+      <c r="CD5" s="33"/>
+      <c r="CE5" s="33"/>
+      <c r="CF5" s="33"/>
+      <c r="CG5" s="33"/>
+      <c r="CH5" s="33"/>
+    </row>
+    <row r="6" spans="1:86" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B6" s="36"/>
+      <c r="C6" s="13"/>
+      <c r="D6" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="F6" s="16"/>
+      <c r="G6" s="17"/>
+      <c r="H6" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="I6" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="J6" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="K6" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="L6" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="M6" s="18" t="s">
+        <v>79</v>
+      </c>
+      <c r="N6" s="18">
+        <v>1</v>
+      </c>
+      <c r="O6" s="18">
+        <v>1612</v>
+      </c>
+      <c r="P6" s="18">
+        <v>90851</v>
+      </c>
+      <c r="Q6" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="R6" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="S6" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="T6" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="U6" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="V6" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="W6" s="21">
+        <f t="shared" ca="1" si="0"/>
+        <v>45794</v>
+      </c>
+      <c r="X6" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="Y6" s="22" t="s">
+        <v>84</v>
+      </c>
+      <c r="Z6" s="23" t="s">
+        <v>85</v>
+      </c>
+      <c r="AA6" s="24" t="s">
+        <v>86</v>
+      </c>
+      <c r="AB6" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="AC6" s="15">
+        <v>870</v>
+      </c>
+      <c r="AD6" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="AE6" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="AF6" s="23" t="s">
+        <v>78</v>
+      </c>
+      <c r="AG6" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="AH6" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="AI6" s="21">
+        <f ca="1">TODAY()+365</f>
+        <v>46190</v>
+      </c>
+      <c r="AJ6" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="AK6" s="25" t="s">
+        <v>93</v>
+      </c>
+      <c r="AL6" s="25" t="s">
+        <v>94</v>
+      </c>
+      <c r="AM6" s="18" t="s">
+        <v>95</v>
+      </c>
+      <c r="AN6" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="AO6" s="24" t="s">
+        <v>97</v>
+      </c>
+      <c r="AP6" s="26" t="s">
+        <v>98</v>
+      </c>
+      <c r="AQ6" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="AR6" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="AS6" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="AT6" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="AU6" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="AV6" s="26" t="s">
+        <v>99</v>
+      </c>
+      <c r="AW6" s="26" t="s">
+        <v>100</v>
+      </c>
+      <c r="AX6" s="27">
+        <v>1234567891</v>
+      </c>
+      <c r="AY6" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="AZ6" s="21" t="s">
+        <v>101</v>
+      </c>
+      <c r="BA6" s="19">
+        <f t="shared" ca="1" si="1"/>
+        <v>45915</v>
+      </c>
+      <c r="BB6" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="BC6" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="BD6" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="BE6" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="BF6" s="19">
+        <f t="shared" ca="1" si="5"/>
+        <v>45794</v>
+      </c>
+      <c r="BG6" s="19">
+        <f t="shared" ca="1" si="6"/>
+        <v>45794</v>
+      </c>
+      <c r="BH6" s="21">
+        <f t="shared" ca="1" si="7"/>
+        <v>46190</v>
+      </c>
+      <c r="BI6" s="28" t="s">
+        <v>74</v>
+      </c>
+      <c r="BJ6" s="29" t="s">
+        <v>106</v>
+      </c>
+      <c r="BK6" s="30">
+        <f t="array" aca="1" ref="BK6:BK7" ca="1">_xlfn.RANDARRAY(2,1,123456789,999999999,TRUE)</f>
+        <v>223053016</v>
+      </c>
+      <c r="BL6" s="31" t="s">
+        <v>107</v>
+      </c>
+      <c r="BM6" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="BN6" s="28" t="s">
+        <v>109</v>
+      </c>
+      <c r="BO6" s="28" t="s">
+        <v>110</v>
+      </c>
+      <c r="BP6" s="32" t="s">
+        <v>78</v>
+      </c>
+      <c r="BQ6" s="28" t="s">
+        <v>111</v>
+      </c>
+      <c r="BR6" s="28" t="s">
+        <v>74</v>
+      </c>
+      <c r="BS6" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="BT6" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="BU6" s="28" t="s">
+        <v>114</v>
+      </c>
+      <c r="BV6" s="28" t="s">
+        <v>115</v>
+      </c>
+      <c r="BW6" s="28" t="s">
+        <v>116</v>
+      </c>
+      <c r="BX6" s="33"/>
+      <c r="BY6" s="33"/>
+      <c r="BZ6" s="34"/>
+      <c r="CA6" s="34"/>
+      <c r="CB6" s="33"/>
+      <c r="CC6" s="33"/>
+      <c r="CD6" s="33"/>
+      <c r="CE6" s="33"/>
+      <c r="CF6" s="33"/>
+      <c r="CG6" s="33"/>
+      <c r="CH6" s="33"/>
+    </row>
+    <row r="7" spans="1:86" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B7" s="35"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="F7" s="16"/>
+      <c r="G7" s="17"/>
+      <c r="H7" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="I7" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="J7" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="K7" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="L7" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="M7" s="18" t="s">
+        <v>79</v>
+      </c>
+      <c r="N7" s="18">
+        <v>1</v>
+      </c>
+      <c r="O7" s="18">
+        <v>1612</v>
+      </c>
+      <c r="P7" s="18">
+        <v>90851</v>
+      </c>
+      <c r="Q7" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="R7" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="S7" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="T7" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="U7" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="V7" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="W7" s="21">
+        <f t="shared" ca="1" si="0"/>
+        <v>45794</v>
+      </c>
+      <c r="X7" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="Y7" s="22" t="s">
+        <v>130</v>
+      </c>
+      <c r="Z7" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="AA7" s="24" t="s">
+        <v>121</v>
+      </c>
+      <c r="AB7" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="AC7" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="AD7" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="AE7" s="15">
+        <v>40</v>
+      </c>
+      <c r="AF7" s="23">
+        <v>40</v>
+      </c>
+      <c r="AG7" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="AH7" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="AI7" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="AJ7" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="AK7" s="25" t="s">
+        <v>123</v>
+      </c>
+      <c r="AL7" s="25" t="s">
+        <v>124</v>
+      </c>
+      <c r="AM7" s="18" t="s">
+        <v>95</v>
+      </c>
+      <c r="AN7" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="AO7" s="24" t="s">
+        <v>125</v>
+      </c>
+      <c r="AP7" s="26" t="s">
+        <v>126</v>
+      </c>
+      <c r="AQ7" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="AR7" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="AS7" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="AT7" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="AU7" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="AV7" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="AW7" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="AX7" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="AY7" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="AZ7" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="BA7" s="19">
+        <f t="shared" ca="1" si="1"/>
+        <v>45915</v>
+      </c>
+      <c r="BB7" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="BC7" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="BD7" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="BE7" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="BF7" s="19">
+        <f t="shared" ca="1" si="5"/>
+        <v>45794</v>
+      </c>
+      <c r="BG7" s="19">
+        <f t="shared" ca="1" si="6"/>
+        <v>45794</v>
+      </c>
+      <c r="BH7" s="21" t="str">
+        <f t="shared" si="7"/>
+        <v>N/A</v>
+      </c>
+      <c r="BI7" s="28" t="s">
+        <v>74</v>
+      </c>
+      <c r="BJ7" s="29" t="s">
+        <v>106</v>
+      </c>
+      <c r="BK7" s="30">
+        <f ca="1"/>
+        <v>671803277</v>
+      </c>
+      <c r="BL7" s="31" t="s">
+        <v>128</v>
+      </c>
+      <c r="BM7" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="BN7" s="28" t="s">
+        <v>109</v>
+      </c>
+      <c r="BO7" s="28" t="s">
+        <v>110</v>
+      </c>
+      <c r="BP7" s="32" t="s">
+        <v>78</v>
+      </c>
+      <c r="BQ7" s="28" t="s">
+        <v>111</v>
+      </c>
+      <c r="BR7" s="28" t="s">
+        <v>74</v>
+      </c>
+      <c r="BS7" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="BT7" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="BU7" s="28" t="s">
+        <v>114</v>
+      </c>
+      <c r="BV7" s="28" t="s">
+        <v>115</v>
+      </c>
+      <c r="BW7" s="28" t="s">
+        <v>116</v>
+      </c>
+      <c r="BX7" s="33"/>
+      <c r="BY7" s="33"/>
+      <c r="BZ7" s="34"/>
+      <c r="CA7" s="34"/>
+      <c r="CB7" s="33"/>
+      <c r="CC7" s="33"/>
+      <c r="CD7" s="33"/>
+      <c r="CE7" s="33"/>
+      <c r="CF7" s="33"/>
+      <c r="CG7" s="33"/>
+      <c r="CH7" s="33"/>
+    </row>
   </sheetData>
-  <dataValidations count="7">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BE2:BE3">
-      <formula1>INDIRECT($H2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BU2:BU3">
-      <formula1>INDIRECT($H2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CB2:CB3">
-      <formula1>INDIRECT($H2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J3">
-      <formula1>INDIRECT($H2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S3">
-      <formula1>INDIRECT($H2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V2:V3">
-      <formula1>INDIRECT($H2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X2:X3">
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BE2:BE7 X2:X7 V2:V7 S2:S7 J2:J7 CB2:CB7 BU2:BU7" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>INDIRECT($H2)</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="U2" r:id="rId1"/>
-    <hyperlink ref="U3" r:id="rId2"/>
+    <hyperlink ref="U2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="U3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="U4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="U5" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="U6" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="U7" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId7"/>
   <headerFooter>
     <oddFooter>&amp;L_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 EXPLEO Internal</oddFooter>
   </headerFooter>

--- a/Data/Hires/Workday_NewHire_Slovakia_Regression_PK17.xlsx
+++ b/Data/Hires/Workday_NewHire_Slovakia_Regression_PK17.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="702" uniqueCount="165">
   <si>
     <t>TestCaseIDs</t>
   </si>
@@ -235,7 +235,7 @@
     <t>Test1</t>
   </si>
   <si>
-    <t>10699678</t>
+    <t>10699801</t>
   </si>
   <si>
     <t>Passed</t>
@@ -247,10 +247,10 @@
     <t>Slovakia</t>
   </si>
   <si>
-    <t>Napoleon</t>
-  </si>
-  <si>
-    <t>Davis</t>
+    <t>Luigi</t>
+  </si>
+  <si>
+    <t>Smitham</t>
   </si>
   <si>
     <t>041/562 66 84</t>
@@ -383,19 +383,19 @@
     <t>Test2</t>
   </si>
   <si>
-    <t>10699623</t>
+    <t>10699802</t>
   </si>
   <si>
     <t>870 Store Management (Wazup Zudimi (9581610))</t>
   </si>
   <si>
-    <t>Peter</t>
-  </si>
-  <si>
-    <t>Wisozk</t>
-  </si>
-  <si>
-    <t>Auto 89162202</t>
+    <t>Daphney</t>
+  </si>
+  <si>
+    <t>Hills</t>
+  </si>
+  <si>
+    <t>Auto 76837525</t>
   </si>
   <si>
     <t>Permanent</t>
@@ -423,6 +423,93 @@
   </si>
   <si>
     <t>Female</t>
+  </si>
+  <si>
+    <t>10699803</t>
+  </si>
+  <si>
+    <t>Santos</t>
+  </si>
+  <si>
+    <t>Runolfsdottir</t>
+  </si>
+  <si>
+    <t>10699804</t>
+  </si>
+  <si>
+    <t>Mathilde</t>
+  </si>
+  <si>
+    <t>Dietrich</t>
+  </si>
+  <si>
+    <t>Auto 31530569</t>
+  </si>
+  <si>
+    <t>Test failed for 'Kris O'Connell' Employee: undefined&amp; find failed Screenshot Path:-&gt;H:\Clone-Workday-Playwright/WorkdayFailedScreenshot/2025-06-20T06-09-29-378Z.png</t>
+  </si>
+  <si>
+    <t>Failed</t>
+  </si>
+  <si>
+    <t>Kris</t>
+  </si>
+  <si>
+    <t>O'Connell</t>
+  </si>
+  <si>
+    <t>10699805</t>
+  </si>
+  <si>
+    <t>Angelita</t>
+  </si>
+  <si>
+    <t>Fritsch</t>
+  </si>
+  <si>
+    <t>Auto 40205967</t>
+  </si>
+  <si>
+    <t>10699807</t>
+  </si>
+  <si>
+    <t>Elfrieda</t>
+  </si>
+  <si>
+    <t>Abshire</t>
+  </si>
+  <si>
+    <t>10699808</t>
+  </si>
+  <si>
+    <t>Kiel</t>
+  </si>
+  <si>
+    <t>Krajcik</t>
+  </si>
+  <si>
+    <t>Auto 13083138</t>
+  </si>
+  <si>
+    <t>10699809</t>
+  </si>
+  <si>
+    <t>Claudie</t>
+  </si>
+  <si>
+    <t>Ankunding</t>
+  </si>
+  <si>
+    <t>10699811</t>
+  </si>
+  <si>
+    <t>Gino</t>
+  </si>
+  <si>
+    <t>Walter</t>
+  </si>
+  <si>
+    <t>Auto 60832082</t>
   </si>
 </sst>
 </file>
@@ -467,7 +554,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -495,6 +582,11 @@
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.7999816888943144"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
       </patternFill>
     </fill>
   </fills>
@@ -593,7 +685,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -701,6 +793,9 @@
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -982,13 +1077,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:CH3"/>
+  <dimension ref="A1:CH11"/>
   <sheetFormatPr defaultRowHeight="15.65" outlineLevelRow="1" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.81640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="58.36328125" style="1" customWidth="1"/>
     <col min="3" max="3" width="9.36328125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="21.453125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="47.1796875" style="1" customWidth="1"/>
     <col min="5" max="5" width="7.54296875" style="1" customWidth="1"/>
     <col min="6" max="6" width="10.453125" style="1" customWidth="1"/>
     <col min="7" max="7" width="11.08984375" style="1" customWidth="1"/>
@@ -1380,8 +1475,8 @@
         <v>81</v>
       </c>
       <c r="W2" s="22">
-        <f t="shared" ref="W2:W3" si="0">TODAY()-31</f>
-        <v>45788</v>
+        <f t="shared" ref="W2:W11" si="0">TODAY()-31</f>
+        <v>45797</v>
       </c>
       <c r="X2" s="19" t="s">
         <v>87</v>
@@ -1418,7 +1513,7 @@
       </c>
       <c r="AI2" s="22">
         <f>TODAY()+365</f>
-        <v>46184</v>
+        <v>46193</v>
       </c>
       <c r="AJ2" s="19" t="s">
         <v>96</v>
@@ -1472,8 +1567,8 @@
         <v>105</v>
       </c>
       <c r="BA2" s="20">
-        <f t="shared" ref="BA2:BA3" si="1">TODAY()+90</f>
-        <v>45909</v>
+        <f t="shared" ref="BA2:BA11" si="1">TODAY()+90</f>
+        <v>45918</v>
       </c>
       <c r="BB2" s="16" t="s">
         <v>106</v>
@@ -1489,15 +1584,15 @@
       </c>
       <c r="BF2" s="20">
         <f t="shared" ref="BF2:BF3" si="2">W2</f>
-        <v>45788</v>
+        <v>45797</v>
       </c>
       <c r="BG2" s="20">
         <f t="shared" ref="BG2:BG3" si="3">W2</f>
-        <v>45788</v>
+        <v>45797</v>
       </c>
       <c r="BH2" s="22">
         <f t="shared" ref="BH2:BH3" si="4">AI2</f>
-        <v>46184</v>
+        <v>46193</v>
       </c>
       <c r="BI2" s="29" t="s">
         <v>76</v>
@@ -1507,7 +1602,7 @@
       </c>
       <c r="BK2" s="31">
         <f t="array" ref="BK2:BK3">_xlfn.RANDARRAY(2,1,123456789,999999999,TRUE)</f>
-        <v>268932618</v>
+        <v>880092345</v>
       </c>
       <c r="BL2" s="32" t="s">
         <v>111</v>
@@ -1626,7 +1721,7 @@
       </c>
       <c r="W3" s="22">
         <f t="shared" si="0"/>
-        <v>45788</v>
+        <v>45797</v>
       </c>
       <c r="X3" s="19" t="s">
         <v>87</v>
@@ -1717,7 +1812,7 @@
       </c>
       <c r="BA3" s="20">
         <f t="shared" si="1"/>
-        <v>45909</v>
+        <v>45918</v>
       </c>
       <c r="BB3" s="16" t="s">
         <v>106</v>
@@ -1733,11 +1828,11 @@
       </c>
       <c r="BF3" s="20">
         <f t="shared" si="2"/>
-        <v>45788</v>
+        <v>45797</v>
       </c>
       <c r="BG3" s="20">
         <f t="shared" si="3"/>
-        <v>45788</v>
+        <v>45797</v>
       </c>
       <c r="BH3" s="22">
         <f t="shared" si="4"/>
@@ -1750,7 +1845,7 @@
         <v>110</v>
       </c>
       <c r="BK3" s="31">
-        <v>443734695</v>
+        <v>861599356</v>
       </c>
       <c r="BL3" s="32" t="s">
         <v>135</v>
@@ -1800,33 +1895,1899 @@
       <c r="CG3" s="34"/>
       <c r="CH3" s="34"/>
     </row>
+    <row r="4" ht="15.65" customHeight="1" spans="2:75" x14ac:dyDescent="0.25">
+      <c r="B4" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="F4" s="17" t="s">
+        <v>137</v>
+      </c>
+      <c r="G4" s="18" t="s">
+        <v>138</v>
+      </c>
+      <c r="H4" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="I4" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="J4" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="K4" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="L4" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="M4" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="N4" s="19">
+        <v>1</v>
+      </c>
+      <c r="O4" s="19">
+        <v>1612</v>
+      </c>
+      <c r="P4" s="19">
+        <v>90851</v>
+      </c>
+      <c r="Q4" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="R4" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="S4" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="T4" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="U4" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="V4" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="W4" s="22">
+        <f t="shared" si="0"/>
+        <v>45797</v>
+      </c>
+      <c r="X4" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="Y4" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="Z4" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="AA4" s="25" t="s">
+        <v>90</v>
+      </c>
+      <c r="AB4" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="AC4" s="16">
+        <v>870</v>
+      </c>
+      <c r="AD4" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="AE4" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="AF4" s="24" t="s">
+        <v>82</v>
+      </c>
+      <c r="AG4" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AH4" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="AI4" s="22">
+        <f t="shared" ref="AI4:AI11" si="5">TODAY()+365</f>
+        <v>46193</v>
+      </c>
+      <c r="AJ4" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="AK4" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="AL4" s="26" t="s">
+        <v>98</v>
+      </c>
+      <c r="AM4" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="AN4" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="AO4" s="25" t="s">
+        <v>101</v>
+      </c>
+      <c r="AP4" s="27" t="s">
+        <v>102</v>
+      </c>
+      <c r="AQ4" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="AR4" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="AS4" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="AT4" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="AU4" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="AV4" s="27" t="s">
+        <v>103</v>
+      </c>
+      <c r="AW4" s="27" t="s">
+        <v>104</v>
+      </c>
+      <c r="AX4" s="28">
+        <v>1234567891</v>
+      </c>
+      <c r="AY4" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="AZ4" s="22" t="s">
+        <v>105</v>
+      </c>
+      <c r="BA4" s="20">
+        <f t="shared" si="1"/>
+        <v>45918</v>
+      </c>
+      <c r="BB4" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="BC4" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="BD4" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="BE4" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="BF4" s="20">
+        <f t="shared" ref="BF4:BF11" si="6">W4</f>
+        <v>45797</v>
+      </c>
+      <c r="BG4" s="20">
+        <f t="shared" ref="BG4:BG11" si="7">W4</f>
+        <v>45797</v>
+      </c>
+      <c r="BH4" s="22">
+        <f t="shared" ref="BH4:BH11" si="8">AI4</f>
+        <v>46193</v>
+      </c>
+      <c r="BI4" s="29" t="s">
+        <v>76</v>
+      </c>
+      <c r="BJ4" s="30" t="s">
+        <v>110</v>
+      </c>
+      <c r="BK4" s="31">
+        <f t="array" ref="BK4:BK5">_xlfn.RANDARRAY(2,1,123456789,999999999,TRUE)</f>
+        <v>567751987</v>
+      </c>
+      <c r="BL4" s="32" t="s">
+        <v>111</v>
+      </c>
+      <c r="BM4" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="BN4" s="29" t="s">
+        <v>113</v>
+      </c>
+      <c r="BO4" s="29" t="s">
+        <v>114</v>
+      </c>
+      <c r="BP4" s="33" t="s">
+        <v>82</v>
+      </c>
+      <c r="BQ4" s="29" t="s">
+        <v>115</v>
+      </c>
+      <c r="BR4" s="29" t="s">
+        <v>76</v>
+      </c>
+      <c r="BS4" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="BT4" s="16" t="s">
+        <v>117</v>
+      </c>
+      <c r="BU4" s="29" t="s">
+        <v>118</v>
+      </c>
+      <c r="BV4" s="29" t="s">
+        <v>119</v>
+      </c>
+      <c r="BW4" s="29" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="5" ht="15.65" customHeight="1" spans="2:75" x14ac:dyDescent="0.25">
+      <c r="B5" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="E5" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="F5" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="G5" s="18" t="s">
+        <v>141</v>
+      </c>
+      <c r="H5" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="I5" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="J5" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="K5" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="L5" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="M5" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="N5" s="19">
+        <v>1</v>
+      </c>
+      <c r="O5" s="19">
+        <v>1612</v>
+      </c>
+      <c r="P5" s="19">
+        <v>90851</v>
+      </c>
+      <c r="Q5" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="R5" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="S5" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="T5" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="U5" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="V5" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="W5" s="22">
+        <f t="shared" si="0"/>
+        <v>45797</v>
+      </c>
+      <c r="X5" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="Y5" s="23" t="s">
+        <v>142</v>
+      </c>
+      <c r="Z5" s="16" t="s">
+        <v>127</v>
+      </c>
+      <c r="AA5" s="25" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB5" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="AC5" s="16" t="s">
+        <v>129</v>
+      </c>
+      <c r="AD5" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="AE5" s="16">
+        <v>40</v>
+      </c>
+      <c r="AF5" s="24">
+        <v>40</v>
+      </c>
+      <c r="AG5" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AH5" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="AI5" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="AJ5" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="AK5" s="26" t="s">
+        <v>130</v>
+      </c>
+      <c r="AL5" s="26" t="s">
+        <v>131</v>
+      </c>
+      <c r="AM5" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="AN5" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="AO5" s="25" t="s">
+        <v>132</v>
+      </c>
+      <c r="AP5" s="27" t="s">
+        <v>133</v>
+      </c>
+      <c r="AQ5" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="AR5" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="AS5" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="AT5" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="AU5" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="AV5" s="27" t="s">
+        <v>82</v>
+      </c>
+      <c r="AW5" s="27" t="s">
+        <v>82</v>
+      </c>
+      <c r="AX5" s="27" t="s">
+        <v>82</v>
+      </c>
+      <c r="AY5" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="AZ5" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="BA5" s="20">
+        <f t="shared" si="1"/>
+        <v>45918</v>
+      </c>
+      <c r="BB5" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="BC5" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="BD5" s="16" t="s">
+        <v>134</v>
+      </c>
+      <c r="BE5" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="BF5" s="20">
+        <f t="shared" si="6"/>
+        <v>45797</v>
+      </c>
+      <c r="BG5" s="20">
+        <f t="shared" si="7"/>
+        <v>45797</v>
+      </c>
+      <c r="BH5" s="22">
+        <f t="shared" si="8"/>
+        <v>NaN</v>
+      </c>
+      <c r="BI5" s="29" t="s">
+        <v>76</v>
+      </c>
+      <c r="BJ5" s="30" t="s">
+        <v>110</v>
+      </c>
+      <c r="BK5" s="31">
+        <v>608465597</v>
+      </c>
+      <c r="BL5" s="32" t="s">
+        <v>135</v>
+      </c>
+      <c r="BM5" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="BN5" s="29" t="s">
+        <v>113</v>
+      </c>
+      <c r="BO5" s="29" t="s">
+        <v>114</v>
+      </c>
+      <c r="BP5" s="33" t="s">
+        <v>82</v>
+      </c>
+      <c r="BQ5" s="29" t="s">
+        <v>115</v>
+      </c>
+      <c r="BR5" s="29" t="s">
+        <v>76</v>
+      </c>
+      <c r="BS5" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="BT5" s="16" t="s">
+        <v>117</v>
+      </c>
+      <c r="BU5" s="29" t="s">
+        <v>118</v>
+      </c>
+      <c r="BV5" s="29" t="s">
+        <v>119</v>
+      </c>
+      <c r="BW5" s="29" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="6" ht="15.65" customHeight="1" spans="2:75" x14ac:dyDescent="0.25">
+      <c r="B6" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C6" s="36" t="s">
+        <v>144</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="E6" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="F6" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="G6" s="18" t="s">
+        <v>146</v>
+      </c>
+      <c r="H6" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="I6" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="J6" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="K6" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="L6" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="M6" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="N6" s="19">
+        <v>1</v>
+      </c>
+      <c r="O6" s="19">
+        <v>1612</v>
+      </c>
+      <c r="P6" s="19">
+        <v>90851</v>
+      </c>
+      <c r="Q6" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="R6" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="S6" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="T6" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="U6" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="V6" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="W6" s="22">
+        <f t="shared" si="0"/>
+        <v>45797</v>
+      </c>
+      <c r="X6" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="Y6" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="Z6" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="AA6" s="25" t="s">
+        <v>90</v>
+      </c>
+      <c r="AB6" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="AC6" s="16">
+        <v>870</v>
+      </c>
+      <c r="AD6" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="AE6" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="AF6" s="24" t="s">
+        <v>82</v>
+      </c>
+      <c r="AG6" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AH6" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="AI6" s="22">
+        <f t="shared" ref="AI6:AI11" si="9">TODAY()+365</f>
+        <v>46193</v>
+      </c>
+      <c r="AJ6" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="AK6" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="AL6" s="26" t="s">
+        <v>98</v>
+      </c>
+      <c r="AM6" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="AN6" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="AO6" s="25" t="s">
+        <v>101</v>
+      </c>
+      <c r="AP6" s="27" t="s">
+        <v>102</v>
+      </c>
+      <c r="AQ6" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="AR6" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="AS6" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="AT6" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="AU6" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="AV6" s="27" t="s">
+        <v>103</v>
+      </c>
+      <c r="AW6" s="27" t="s">
+        <v>104</v>
+      </c>
+      <c r="AX6" s="28">
+        <v>1234567891</v>
+      </c>
+      <c r="AY6" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="AZ6" s="22" t="s">
+        <v>105</v>
+      </c>
+      <c r="BA6" s="20">
+        <f t="shared" si="1"/>
+        <v>45918</v>
+      </c>
+      <c r="BB6" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="BC6" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="BD6" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="BE6" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="BF6" s="20">
+        <f t="shared" si="6"/>
+        <v>45797</v>
+      </c>
+      <c r="BG6" s="20">
+        <f t="shared" si="7"/>
+        <v>45797</v>
+      </c>
+      <c r="BH6" s="22">
+        <f t="shared" si="8"/>
+        <v>46193</v>
+      </c>
+      <c r="BI6" s="29" t="s">
+        <v>76</v>
+      </c>
+      <c r="BJ6" s="30" t="s">
+        <v>110</v>
+      </c>
+      <c r="BK6" s="31">
+        <f t="array" ref="BK6:BK7">_xlfn.RANDARRAY(2,1,123456789,999999999,TRUE)</f>
+        <v>859357108</v>
+      </c>
+      <c r="BL6" s="32" t="s">
+        <v>111</v>
+      </c>
+      <c r="BM6" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="BN6" s="29" t="s">
+        <v>113</v>
+      </c>
+      <c r="BO6" s="29" t="s">
+        <v>114</v>
+      </c>
+      <c r="BP6" s="33" t="s">
+        <v>82</v>
+      </c>
+      <c r="BQ6" s="29" t="s">
+        <v>115</v>
+      </c>
+      <c r="BR6" s="29" t="s">
+        <v>76</v>
+      </c>
+      <c r="BS6" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="BT6" s="16" t="s">
+        <v>117</v>
+      </c>
+      <c r="BU6" s="29" t="s">
+        <v>118</v>
+      </c>
+      <c r="BV6" s="29" t="s">
+        <v>119</v>
+      </c>
+      <c r="BW6" s="29" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="7" ht="15.65" customHeight="1" spans="2:75" x14ac:dyDescent="0.25">
+      <c r="B7" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="F7" s="17" t="s">
+        <v>148</v>
+      </c>
+      <c r="G7" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="H7" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="I7" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="J7" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="K7" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="L7" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="M7" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="N7" s="19">
+        <v>1</v>
+      </c>
+      <c r="O7" s="19">
+        <v>1612</v>
+      </c>
+      <c r="P7" s="19">
+        <v>90851</v>
+      </c>
+      <c r="Q7" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="R7" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="S7" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="T7" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="U7" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="V7" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="W7" s="22">
+        <f t="shared" si="0"/>
+        <v>45797</v>
+      </c>
+      <c r="X7" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="Y7" s="23" t="s">
+        <v>150</v>
+      </c>
+      <c r="Z7" s="16" t="s">
+        <v>127</v>
+      </c>
+      <c r="AA7" s="25" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB7" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="AC7" s="16" t="s">
+        <v>129</v>
+      </c>
+      <c r="AD7" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="AE7" s="16">
+        <v>40</v>
+      </c>
+      <c r="AF7" s="24">
+        <v>40</v>
+      </c>
+      <c r="AG7" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AH7" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="AI7" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="AJ7" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="AK7" s="26" t="s">
+        <v>130</v>
+      </c>
+      <c r="AL7" s="26" t="s">
+        <v>131</v>
+      </c>
+      <c r="AM7" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="AN7" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="AO7" s="25" t="s">
+        <v>132</v>
+      </c>
+      <c r="AP7" s="27" t="s">
+        <v>133</v>
+      </c>
+      <c r="AQ7" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="AR7" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="AS7" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="AT7" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="AU7" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="AV7" s="27" t="s">
+        <v>82</v>
+      </c>
+      <c r="AW7" s="27" t="s">
+        <v>82</v>
+      </c>
+      <c r="AX7" s="27" t="s">
+        <v>82</v>
+      </c>
+      <c r="AY7" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="AZ7" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="BA7" s="20">
+        <f t="shared" si="1"/>
+        <v>45918</v>
+      </c>
+      <c r="BB7" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="BC7" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="BD7" s="16" t="s">
+        <v>134</v>
+      </c>
+      <c r="BE7" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="BF7" s="20">
+        <f t="shared" si="6"/>
+        <v>45797</v>
+      </c>
+      <c r="BG7" s="20">
+        <f t="shared" si="7"/>
+        <v>45797</v>
+      </c>
+      <c r="BH7" s="22">
+        <f t="shared" si="8"/>
+        <v>NaN</v>
+      </c>
+      <c r="BI7" s="29" t="s">
+        <v>76</v>
+      </c>
+      <c r="BJ7" s="30" t="s">
+        <v>110</v>
+      </c>
+      <c r="BK7" s="31">
+        <v>586844631</v>
+      </c>
+      <c r="BL7" s="32" t="s">
+        <v>135</v>
+      </c>
+      <c r="BM7" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="BN7" s="29" t="s">
+        <v>113</v>
+      </c>
+      <c r="BO7" s="29" t="s">
+        <v>114</v>
+      </c>
+      <c r="BP7" s="33" t="s">
+        <v>82</v>
+      </c>
+      <c r="BQ7" s="29" t="s">
+        <v>115</v>
+      </c>
+      <c r="BR7" s="29" t="s">
+        <v>76</v>
+      </c>
+      <c r="BS7" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="BT7" s="16" t="s">
+        <v>117</v>
+      </c>
+      <c r="BU7" s="29" t="s">
+        <v>118</v>
+      </c>
+      <c r="BV7" s="29" t="s">
+        <v>119</v>
+      </c>
+      <c r="BW7" s="29" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="8" ht="15.65" customHeight="1" spans="2:75" x14ac:dyDescent="0.25">
+      <c r="B8" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="E8" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="F8" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="G8" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="H8" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="I8" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="J8" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="K8" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="L8" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="M8" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="N8" s="19">
+        <v>1</v>
+      </c>
+      <c r="O8" s="19">
+        <v>1612</v>
+      </c>
+      <c r="P8" s="19">
+        <v>90851</v>
+      </c>
+      <c r="Q8" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="R8" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="S8" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="T8" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="U8" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="V8" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="W8" s="22">
+        <f t="shared" si="0"/>
+        <v>45797</v>
+      </c>
+      <c r="X8" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="Y8" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="Z8" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="AA8" s="25" t="s">
+        <v>90</v>
+      </c>
+      <c r="AB8" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="AC8" s="16">
+        <v>870</v>
+      </c>
+      <c r="AD8" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="AE8" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="AF8" s="24" t="s">
+        <v>82</v>
+      </c>
+      <c r="AG8" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AH8" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="AI8" s="22">
+        <f t="shared" ref="AI8:AI11" si="10">TODAY()+365</f>
+        <v>46193</v>
+      </c>
+      <c r="AJ8" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="AK8" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="AL8" s="26" t="s">
+        <v>98</v>
+      </c>
+      <c r="AM8" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="AN8" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="AO8" s="25" t="s">
+        <v>101</v>
+      </c>
+      <c r="AP8" s="27" t="s">
+        <v>102</v>
+      </c>
+      <c r="AQ8" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="AR8" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="AS8" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="AT8" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="AU8" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="AV8" s="27" t="s">
+        <v>103</v>
+      </c>
+      <c r="AW8" s="27" t="s">
+        <v>104</v>
+      </c>
+      <c r="AX8" s="28">
+        <v>1234567891</v>
+      </c>
+      <c r="AY8" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="AZ8" s="22" t="s">
+        <v>105</v>
+      </c>
+      <c r="BA8" s="20">
+        <f t="shared" si="1"/>
+        <v>45918</v>
+      </c>
+      <c r="BB8" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="BC8" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="BD8" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="BE8" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="BF8" s="20">
+        <f t="shared" si="6"/>
+        <v>45797</v>
+      </c>
+      <c r="BG8" s="20">
+        <f t="shared" si="7"/>
+        <v>45797</v>
+      </c>
+      <c r="BH8" s="22">
+        <f t="shared" si="8"/>
+        <v>46193</v>
+      </c>
+      <c r="BI8" s="29" t="s">
+        <v>76</v>
+      </c>
+      <c r="BJ8" s="30" t="s">
+        <v>110</v>
+      </c>
+      <c r="BK8" s="31">
+        <f t="array" ref="BK8:BK9">_xlfn.RANDARRAY(2,1,123456789,999999999,TRUE)</f>
+        <v>819890654</v>
+      </c>
+      <c r="BL8" s="32" t="s">
+        <v>111</v>
+      </c>
+      <c r="BM8" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="BN8" s="29" t="s">
+        <v>113</v>
+      </c>
+      <c r="BO8" s="29" t="s">
+        <v>114</v>
+      </c>
+      <c r="BP8" s="33" t="s">
+        <v>82</v>
+      </c>
+      <c r="BQ8" s="29" t="s">
+        <v>115</v>
+      </c>
+      <c r="BR8" s="29" t="s">
+        <v>76</v>
+      </c>
+      <c r="BS8" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="BT8" s="16" t="s">
+        <v>117</v>
+      </c>
+      <c r="BU8" s="29" t="s">
+        <v>118</v>
+      </c>
+      <c r="BV8" s="29" t="s">
+        <v>119</v>
+      </c>
+      <c r="BW8" s="29" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="9" ht="15.65" customHeight="1" spans="2:75" x14ac:dyDescent="0.25">
+      <c r="B9" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="E9" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="F9" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="G9" s="18" t="s">
+        <v>156</v>
+      </c>
+      <c r="H9" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="I9" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="J9" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="K9" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="L9" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="M9" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="N9" s="19">
+        <v>1</v>
+      </c>
+      <c r="O9" s="19">
+        <v>1612</v>
+      </c>
+      <c r="P9" s="19">
+        <v>90851</v>
+      </c>
+      <c r="Q9" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="R9" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="S9" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="T9" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="U9" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="V9" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="W9" s="22">
+        <f t="shared" si="0"/>
+        <v>45797</v>
+      </c>
+      <c r="X9" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="Y9" s="23" t="s">
+        <v>157</v>
+      </c>
+      <c r="Z9" s="16" t="s">
+        <v>127</v>
+      </c>
+      <c r="AA9" s="25" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB9" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="AC9" s="16" t="s">
+        <v>129</v>
+      </c>
+      <c r="AD9" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="AE9" s="16">
+        <v>40</v>
+      </c>
+      <c r="AF9" s="24">
+        <v>40</v>
+      </c>
+      <c r="AG9" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AH9" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="AI9" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="AJ9" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="AK9" s="26" t="s">
+        <v>130</v>
+      </c>
+      <c r="AL9" s="26" t="s">
+        <v>131</v>
+      </c>
+      <c r="AM9" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="AN9" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="AO9" s="25" t="s">
+        <v>132</v>
+      </c>
+      <c r="AP9" s="27" t="s">
+        <v>133</v>
+      </c>
+      <c r="AQ9" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="AR9" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="AS9" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="AT9" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="AU9" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="AV9" s="27" t="s">
+        <v>82</v>
+      </c>
+      <c r="AW9" s="27" t="s">
+        <v>82</v>
+      </c>
+      <c r="AX9" s="27" t="s">
+        <v>82</v>
+      </c>
+      <c r="AY9" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="AZ9" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="BA9" s="20">
+        <f t="shared" si="1"/>
+        <v>45918</v>
+      </c>
+      <c r="BB9" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="BC9" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="BD9" s="16" t="s">
+        <v>134</v>
+      </c>
+      <c r="BE9" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="BF9" s="20">
+        <f t="shared" si="6"/>
+        <v>45797</v>
+      </c>
+      <c r="BG9" s="20">
+        <f t="shared" si="7"/>
+        <v>45797</v>
+      </c>
+      <c r="BH9" s="22">
+        <f t="shared" si="8"/>
+        <v>NaN</v>
+      </c>
+      <c r="BI9" s="29" t="s">
+        <v>76</v>
+      </c>
+      <c r="BJ9" s="30" t="s">
+        <v>110</v>
+      </c>
+      <c r="BK9" s="31">
+        <v>787866121</v>
+      </c>
+      <c r="BL9" s="32" t="s">
+        <v>135</v>
+      </c>
+      <c r="BM9" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="BN9" s="29" t="s">
+        <v>113</v>
+      </c>
+      <c r="BO9" s="29" t="s">
+        <v>114</v>
+      </c>
+      <c r="BP9" s="33" t="s">
+        <v>82</v>
+      </c>
+      <c r="BQ9" s="29" t="s">
+        <v>115</v>
+      </c>
+      <c r="BR9" s="29" t="s">
+        <v>76</v>
+      </c>
+      <c r="BS9" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="BT9" s="16" t="s">
+        <v>117</v>
+      </c>
+      <c r="BU9" s="29" t="s">
+        <v>118</v>
+      </c>
+      <c r="BV9" s="29" t="s">
+        <v>119</v>
+      </c>
+      <c r="BW9" s="29" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="10" ht="15.65" customHeight="1" spans="2:75" x14ac:dyDescent="0.25">
+      <c r="B10" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="E10" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="F10" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="G10" s="18" t="s">
+        <v>160</v>
+      </c>
+      <c r="H10" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="I10" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="J10" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="K10" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="L10" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="M10" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="N10" s="19">
+        <v>1</v>
+      </c>
+      <c r="O10" s="19">
+        <v>1612</v>
+      </c>
+      <c r="P10" s="19">
+        <v>90851</v>
+      </c>
+      <c r="Q10" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="R10" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="S10" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="T10" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="U10" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="V10" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="W10" s="22">
+        <f t="shared" si="0"/>
+        <v>45797</v>
+      </c>
+      <c r="X10" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="Y10" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="Z10" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="AA10" s="25" t="s">
+        <v>90</v>
+      </c>
+      <c r="AB10" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="AC10" s="16">
+        <v>870</v>
+      </c>
+      <c r="AD10" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="AE10" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="AF10" s="24" t="s">
+        <v>82</v>
+      </c>
+      <c r="AG10" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AH10" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="AI10" s="22">
+        <f t="shared" ref="AI10:AI11" si="11">TODAY()+365</f>
+        <v>46193</v>
+      </c>
+      <c r="AJ10" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="AK10" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="AL10" s="26" t="s">
+        <v>98</v>
+      </c>
+      <c r="AM10" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="AN10" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="AO10" s="25" t="s">
+        <v>101</v>
+      </c>
+      <c r="AP10" s="27" t="s">
+        <v>102</v>
+      </c>
+      <c r="AQ10" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="AR10" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="AS10" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="AT10" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="AU10" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="AV10" s="27" t="s">
+        <v>103</v>
+      </c>
+      <c r="AW10" s="27" t="s">
+        <v>104</v>
+      </c>
+      <c r="AX10" s="28">
+        <v>1234567891</v>
+      </c>
+      <c r="AY10" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="AZ10" s="22" t="s">
+        <v>105</v>
+      </c>
+      <c r="BA10" s="20">
+        <f t="shared" si="1"/>
+        <v>45918</v>
+      </c>
+      <c r="BB10" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="BC10" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="BD10" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="BE10" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="BF10" s="20">
+        <f t="shared" si="6"/>
+        <v>45797</v>
+      </c>
+      <c r="BG10" s="20">
+        <f t="shared" si="7"/>
+        <v>45797</v>
+      </c>
+      <c r="BH10" s="22">
+        <f t="shared" si="8"/>
+        <v>46193</v>
+      </c>
+      <c r="BI10" s="29" t="s">
+        <v>76</v>
+      </c>
+      <c r="BJ10" s="30" t="s">
+        <v>110</v>
+      </c>
+      <c r="BK10" s="31">
+        <f t="array" ref="BK10:BK11">_xlfn.RANDARRAY(2,1,123456789,999999999,TRUE)</f>
+        <v>247845841</v>
+      </c>
+      <c r="BL10" s="32" t="s">
+        <v>111</v>
+      </c>
+      <c r="BM10" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="BN10" s="29" t="s">
+        <v>113</v>
+      </c>
+      <c r="BO10" s="29" t="s">
+        <v>114</v>
+      </c>
+      <c r="BP10" s="33" t="s">
+        <v>82</v>
+      </c>
+      <c r="BQ10" s="29" t="s">
+        <v>115</v>
+      </c>
+      <c r="BR10" s="29" t="s">
+        <v>76</v>
+      </c>
+      <c r="BS10" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="BT10" s="16" t="s">
+        <v>117</v>
+      </c>
+      <c r="BU10" s="29" t="s">
+        <v>118</v>
+      </c>
+      <c r="BV10" s="29" t="s">
+        <v>119</v>
+      </c>
+      <c r="BW10" s="29" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="11" ht="15.65" customHeight="1" spans="2:75" x14ac:dyDescent="0.25">
+      <c r="B11" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="E11" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="F11" s="17" t="s">
+        <v>162</v>
+      </c>
+      <c r="G11" s="18" t="s">
+        <v>163</v>
+      </c>
+      <c r="H11" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="I11" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="J11" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="K11" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="L11" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="M11" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="N11" s="19">
+        <v>1</v>
+      </c>
+      <c r="O11" s="19">
+        <v>1612</v>
+      </c>
+      <c r="P11" s="19">
+        <v>90851</v>
+      </c>
+      <c r="Q11" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="R11" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="S11" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="T11" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="U11" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="V11" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="W11" s="22">
+        <f t="shared" si="0"/>
+        <v>45797</v>
+      </c>
+      <c r="X11" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="Y11" s="23" t="s">
+        <v>164</v>
+      </c>
+      <c r="Z11" s="16" t="s">
+        <v>127</v>
+      </c>
+      <c r="AA11" s="25" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB11" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="AC11" s="16" t="s">
+        <v>129</v>
+      </c>
+      <c r="AD11" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="AE11" s="16">
+        <v>40</v>
+      </c>
+      <c r="AF11" s="24">
+        <v>40</v>
+      </c>
+      <c r="AG11" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AH11" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="AI11" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="AJ11" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="AK11" s="26" t="s">
+        <v>130</v>
+      </c>
+      <c r="AL11" s="26" t="s">
+        <v>131</v>
+      </c>
+      <c r="AM11" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="AN11" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="AO11" s="25" t="s">
+        <v>132</v>
+      </c>
+      <c r="AP11" s="27" t="s">
+        <v>133</v>
+      </c>
+      <c r="AQ11" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="AR11" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="AS11" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="AT11" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="AU11" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="AV11" s="27" t="s">
+        <v>82</v>
+      </c>
+      <c r="AW11" s="27" t="s">
+        <v>82</v>
+      </c>
+      <c r="AX11" s="27" t="s">
+        <v>82</v>
+      </c>
+      <c r="AY11" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="AZ11" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="BA11" s="20">
+        <f t="shared" si="1"/>
+        <v>45918</v>
+      </c>
+      <c r="BB11" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="BC11" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="BD11" s="16" t="s">
+        <v>134</v>
+      </c>
+      <c r="BE11" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="BF11" s="20">
+        <f t="shared" si="6"/>
+        <v>45797</v>
+      </c>
+      <c r="BG11" s="20">
+        <f t="shared" si="7"/>
+        <v>45797</v>
+      </c>
+      <c r="BH11" s="22">
+        <f t="shared" si="8"/>
+        <v>NaN</v>
+      </c>
+      <c r="BI11" s="29" t="s">
+        <v>76</v>
+      </c>
+      <c r="BJ11" s="30" t="s">
+        <v>110</v>
+      </c>
+      <c r="BK11" s="31">
+        <v>919022363</v>
+      </c>
+      <c r="BL11" s="32" t="s">
+        <v>135</v>
+      </c>
+      <c r="BM11" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="BN11" s="29" t="s">
+        <v>113</v>
+      </c>
+      <c r="BO11" s="29" t="s">
+        <v>114</v>
+      </c>
+      <c r="BP11" s="33" t="s">
+        <v>82</v>
+      </c>
+      <c r="BQ11" s="29" t="s">
+        <v>115</v>
+      </c>
+      <c r="BR11" s="29" t="s">
+        <v>76</v>
+      </c>
+      <c r="BS11" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="BT11" s="16" t="s">
+        <v>117</v>
+      </c>
+      <c r="BU11" s="29" t="s">
+        <v>118</v>
+      </c>
+      <c r="BV11" s="29" t="s">
+        <v>119</v>
+      </c>
+      <c r="BW11" s="29" t="s">
+        <v>120</v>
+      </c>
+    </row>
   </sheetData>
-  <dataValidations count="7">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BE2:BE3">
+  <dataValidations count="13">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BE10:BE11">
       <formula1>INDIRECT($H2)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BU2:BU3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BE2:BE11">
+      <formula1>INDIRECT($H2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BU10:BU11">
+      <formula1>INDIRECT($H2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BU2:BU11">
       <formula1>INDIRECT($H2)</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CB2:CB3">
       <formula1>INDIRECT($H2)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J10:J11">
       <formula1>INDIRECT($H2)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J11">
       <formula1>INDIRECT($H2)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V2:V3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S10:S11">
       <formula1>INDIRECT($H2)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X2:X3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S11">
+      <formula1>INDIRECT($H2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V10:V11">
+      <formula1>INDIRECT($H2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V2:V11">
+      <formula1>INDIRECT($H2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X10:X11">
+      <formula1>INDIRECT($H2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X2:X11">
       <formula1>INDIRECT($H2)</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="U2" r:id="rId1"/>
     <hyperlink ref="U3" r:id="rId2"/>
+    <hyperlink ref="U4" r:id="rId3"/>
+    <hyperlink ref="U5" r:id="rId4"/>
+    <hyperlink ref="U6" r:id="rId5"/>
+    <hyperlink ref="U7" r:id="rId6"/>
+    <hyperlink ref="U8" r:id="rId7"/>
+    <hyperlink ref="U9" r:id="rId8"/>
+    <hyperlink ref="U10" r:id="rId9"/>
+    <hyperlink ref="U11" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>

--- a/Data/Hires/Workday_NewHire_Slovakia_Regression_PK17.xlsx
+++ b/Data/Hires/Workday_NewHire_Slovakia_Regression_PK17.xlsx
@@ -1,35 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{B0A6869C-43F5-4F1A-B29E-69CFE32C2114}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet2" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Sheet2" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="136">
   <si>
     <t>TestCaseIDs</t>
   </si>
@@ -250,7 +235,7 @@
     <t>Test1</t>
   </si>
   <si>
-    <t>10700259</t>
+    <t>10700459</t>
   </si>
   <si>
     <t>Passed</t>
@@ -262,10 +247,10 @@
     <t>Slovakia</t>
   </si>
   <si>
-    <t>Kyla</t>
-  </si>
-  <si>
-    <t>Lubowitz</t>
+    <t>Macie</t>
+  </si>
+  <si>
+    <t>Labadie</t>
   </si>
   <si>
     <t>041/562 66 84</t>
@@ -334,7 +319,7 @@
     <t>SK Monthly</t>
   </si>
   <si>
-    <t>Meal Voucher Card </t>
+    <t xml:space="preserve">Meal Voucher Card </t>
   </si>
   <si>
     <t>Všeobecná zdrav. Poisť.</t>
@@ -398,13 +383,19 @@
     <t>Test2</t>
   </si>
   <si>
+    <t>10700473</t>
+  </si>
+  <si>
     <t>870 Store Management (Wazup Zudimi (9581610))</t>
   </si>
   <si>
-    <t>Delphine</t>
-  </si>
-  <si>
-    <t>Auto 96270717</t>
+    <t>Hilma</t>
+  </si>
+  <si>
+    <t>Bruen</t>
+  </si>
+  <si>
+    <t>Auto 98919828</t>
   </si>
   <si>
     <t>Permanent</t>
@@ -437,54 +428,54 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
+      <family val="2"/>
+      <scheme val="minor"/>
       <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
+      <color theme="1"/>
+      <family val="2"/>
       <sz val="14"/>
-      <color theme="1"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <u/>
+      <family val="2"/>
+      <scheme val="minor"/>
       <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -493,7 +484,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
+        <fgColor theme="5" tint="0.5999938962981048"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -505,14 +496,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
+        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
+        <fgColor theme="5" tint="0.7999816888943144"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00FF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -531,27 +527,17 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
@@ -561,25 +547,15 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
+      <top style="thin"/>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
@@ -590,9 +566,7 @@
         <color indexed="64"/>
       </right>
       <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
@@ -602,49 +576,31 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
+      <top style="thin"/>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
+      <left style="thin"/>
+      <right style="thin"/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
+      <left style="thin"/>
+      <right style="thin"/>
       <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
@@ -687,17 +643,17 @@
     <xf numFmtId="49" fontId="2" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
@@ -712,7 +668,7 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -757,7 +713,7 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -1039,9 +995,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:CH3"/>
-  <sheetFormatPr defaultRowHeight="15.65" customHeight="1" outlineLevelRow="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15.65" outlineLevelRow="1" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.81640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="58.36328125" style="1" customWidth="1"/>
@@ -1132,7 +1088,7 @@
     <col min="87" max="87" width="8.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:86" s="3" customFormat="1" ht="14.5" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="14.5" customHeight="1" spans="1:86" s="3" customFormat="1" x14ac:dyDescent="0.25" outlineLevel="1" collapsed="1">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1370,14 +1326,14 @@
       <c r="CG1" s="11"/>
       <c r="CH1" s="12"/>
     </row>
-    <row r="2" spans="1:86" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" ht="15.65" customHeight="1" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>72</v>
       </c>
       <c r="B2" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="C2" s="35" t="s">
+      <c r="C2" s="13" t="s">
         <v>74</v>
       </c>
       <c r="D2" s="14" t="s">
@@ -1438,8 +1394,8 @@
         <v>81</v>
       </c>
       <c r="W2" s="21">
-        <f t="shared" ref="W2:W3" ca="1" si="0">TODAY()-31</f>
-        <v>45824</v>
+        <f t="shared" ref="W2:W3" si="0">TODAY()-31</f>
+        <v>45844</v>
       </c>
       <c r="X2" s="18" t="s">
         <v>87</v>
@@ -1475,8 +1431,8 @@
         <v>95</v>
       </c>
       <c r="AI2" s="21">
-        <f ca="1">TODAY()+365</f>
-        <v>46220</v>
+        <f>TODAY()+365</f>
+        <v>46240</v>
       </c>
       <c r="AJ2" s="18" t="s">
         <v>96</v>
@@ -1530,8 +1486,8 @@
         <v>105</v>
       </c>
       <c r="BA2" s="19">
-        <f t="shared" ref="BA2:BA3" ca="1" si="1">TODAY()+90</f>
-        <v>45945</v>
+        <f t="shared" ref="BA2:BA3" si="1">TODAY()+90</f>
+        <v>45965</v>
       </c>
       <c r="BB2" s="15" t="s">
         <v>106</v>
@@ -1546,16 +1502,16 @@
         <v>109</v>
       </c>
       <c r="BF2" s="19">
-        <f t="shared" ref="BF2:BF3" ca="1" si="2">W2</f>
-        <v>45824</v>
+        <f t="shared" ref="BF2:BF3" si="2">W2</f>
+        <v>45844</v>
       </c>
       <c r="BG2" s="19">
-        <f t="shared" ref="BG2:BG3" ca="1" si="3">W2</f>
-        <v>45824</v>
+        <f t="shared" ref="BG2:BG3" si="3">W2</f>
+        <v>45844</v>
       </c>
       <c r="BH2" s="21">
-        <f t="shared" ref="BH2:BH3" ca="1" si="4">AI2</f>
-        <v>46220</v>
+        <f t="shared" ref="BH2:BH3" si="4">AI2</f>
+        <v>46240</v>
       </c>
       <c r="BI2" s="28" t="s">
         <v>76</v>
@@ -1564,8 +1520,8 @@
         <v>110</v>
       </c>
       <c r="BK2" s="30">
-        <f t="array" aca="1" ref="BK2:BK3" ca="1">_xlfn.RANDARRAY(2,1,123456789,999999999,TRUE)</f>
-        <v>627374172</v>
+        <f t="array" ref="BK2:BK3">_xlfn.RANDARRAY(2,1,123456789,999999999,TRUE)</f>
+        <v>778144741</v>
       </c>
       <c r="BL2" s="31" t="s">
         <v>111</v>
@@ -1615,27 +1571,27 @@
       <c r="CG2" s="33"/>
       <c r="CH2" s="33"/>
     </row>
-    <row r="3" spans="1:86" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" ht="15.65" customHeight="1" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="B3" s="13">
-        <v>10700286</v>
+      <c r="B3" s="13" t="s">
+        <v>122</v>
       </c>
       <c r="C3" s="35" t="s">
         <v>74</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E3" s="15" t="s">
         <v>76</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G3" s="17" t="s">
-        <v>78</v>
+        <v>125</v>
       </c>
       <c r="H3" s="15" t="s">
         <v>79</v>
@@ -1683,26 +1639,26 @@
         <v>81</v>
       </c>
       <c r="W3" s="21">
-        <f t="shared" ca="1" si="0"/>
-        <v>45824</v>
+        <f t="shared" si="0"/>
+        <v>45844</v>
       </c>
       <c r="X3" s="18" t="s">
         <v>87</v>
       </c>
       <c r="Y3" s="22" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="Z3" s="15" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="AA3" s="24" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="AB3" s="19" t="s">
         <v>91</v>
       </c>
       <c r="AC3" s="15" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="AD3" s="15" t="s">
         <v>92</v>
@@ -1726,10 +1682,10 @@
         <v>96</v>
       </c>
       <c r="AK3" s="25" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="AL3" s="25" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="AM3" s="18" t="s">
         <v>99</v>
@@ -1738,10 +1694,10 @@
         <v>100</v>
       </c>
       <c r="AO3" s="24" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="AP3" s="26" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="AQ3" s="15" t="s">
         <v>88</v>
@@ -1774,8 +1730,8 @@
         <v>82</v>
       </c>
       <c r="BA3" s="19">
-        <f t="shared" ca="1" si="1"/>
-        <v>45945</v>
+        <f t="shared" si="1"/>
+        <v>45965</v>
       </c>
       <c r="BB3" s="15" t="s">
         <v>106</v>
@@ -1784,22 +1740,22 @@
         <v>107</v>
       </c>
       <c r="BD3" s="15" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="BE3" s="18" t="s">
         <v>109</v>
       </c>
       <c r="BF3" s="19">
-        <f t="shared" ca="1" si="2"/>
-        <v>45824</v>
+        <f t="shared" si="2"/>
+        <v>45844</v>
       </c>
       <c r="BG3" s="19">
-        <f t="shared" ca="1" si="3"/>
-        <v>45824</v>
-      </c>
-      <c r="BH3" s="21" t="str">
+        <f t="shared" si="3"/>
+        <v>45844</v>
+      </c>
+      <c r="BH3" s="21">
         <f t="shared" si="4"/>
-        <v>N/A</v>
+        <v>NaN</v>
       </c>
       <c r="BI3" s="28" t="s">
         <v>76</v>
@@ -1808,11 +1764,10 @@
         <v>110</v>
       </c>
       <c r="BK3" s="30">
-        <f ca="1"/>
-        <v>379704720</v>
+        <v>642452525</v>
       </c>
       <c r="BL3" s="31" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="BM3" s="19" t="s">
         <v>112</v>
@@ -1860,17 +1815,35 @@
       <c r="CH3" s="33"/>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BE2:BE3 X2:X3 V2:V3 S2:S3 J2:J3 CB2:CB3 BU2:BU3" xr:uid="{00000000-0002-0000-0000-000000000000}">
+  <dataValidations count="7">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BE2:BE3">
+      <formula1>INDIRECT($H2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BU2:BU3">
+      <formula1>INDIRECT($H2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CB2:CB3">
+      <formula1>INDIRECT($H2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J3">
+      <formula1>INDIRECT($H2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S3">
+      <formula1>INDIRECT($H2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V2:V3">
+      <formula1>INDIRECT($H2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X2:X3">
       <formula1>INDIRECT($H2)</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="U2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="U3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="U2" r:id="rId1"/>
+    <hyperlink ref="U3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
   <headerFooter>
     <oddFooter>&amp;L_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 EXPLEO Internal</oddFooter>
   </headerFooter>
